--- a/2026/ANATOLE FRANCE/Junio/ANATOLE-Junio.xlsx
+++ b/2026/ANATOLE FRANCE/Junio/ANATOLE-Junio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817E97DB-EB4E-4AAD-8042-326EE698C6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDD8CEC-8002-48D2-9022-F23A22EE0068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -496,15 +496,6 @@
     <t>Fracchia garcia Sebastian ezequiel</t>
   </si>
   <si>
-    <t>VTO 18/06</t>
-  </si>
-  <si>
-    <t>PERÍODO: MAYO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de MAYO</t>
-  </si>
-  <si>
     <t>Cuello Natalia - Servicio de emergencia - Desobstruccion de colectora cloacal</t>
   </si>
   <si>
@@ -514,36 +505,18 @@
     <t>Casa Ruan - Compra de materiales electricos</t>
   </si>
   <si>
-    <t>Transf 21/05</t>
-  </si>
-  <si>
     <t>Urbeco - Anticipo de cambio de tapa y marco en TQ cisterna de bombeo - Anticipo Reparacion e impermeabilizacion interna de respectiva cuba</t>
   </si>
   <si>
-    <t>Transf 18/05</t>
-  </si>
-  <si>
     <t>Transf 14/05</t>
   </si>
   <si>
     <t>Transf 06/05</t>
   </si>
   <si>
-    <t>Transf 08/05</t>
-  </si>
-  <si>
-    <t>Doartero Julio - Reparacion de perdida bajo mesada - Mano de obra y materiales</t>
-  </si>
-  <si>
-    <t>Transf 07/05</t>
-  </si>
-  <si>
     <t>Transf 11/05</t>
   </si>
   <si>
-    <t>Honorarios administracion - Marzo y Abril - Se adeuda Mayo</t>
-  </si>
-  <si>
     <t>Transf 12/05</t>
   </si>
   <si>
@@ -553,9 +526,6 @@
     <t>Cuello Natalia - Desobstruccion columna baño 4C</t>
   </si>
   <si>
-    <t>Servisur - Retiro de tortugas plasticas en zotano - Instalacion de cable en bastidor y llave de un punto - Cambio de lampras eantiexplosivas sala de gas</t>
-  </si>
-  <si>
     <t>Transf 26/05</t>
   </si>
   <si>
@@ -569,6 +539,36 @@
   </si>
   <si>
     <t>Barreiro Cristina</t>
+  </si>
+  <si>
+    <t>VTO 17/07</t>
+  </si>
+  <si>
+    <t>PERÍODO: JUNIO</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de JUNIO</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - MAYO - Se adeuda JUNIO</t>
+  </si>
+  <si>
+    <t>Transf 04/06</t>
+  </si>
+  <si>
+    <t>Urbeco - Saldo de cambio de tapa y marco en TQ cisterna de bombeo - Saldo Reparacion e impermeabilizacion interna de respectiva cuba</t>
+  </si>
+  <si>
+    <t>Transf 05/06</t>
+  </si>
+  <si>
+    <t>Transf 02/06</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Transf 18/06</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1275,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1541,19 +1541,36 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1566,30 +1583,57 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1605,54 +1649,6 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1671,6 +1667,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2052,11 +2054,11 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
-      <c r="B1" s="192" t="s">
+      <c r="B1" s="197" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
+      <c r="C1" s="197"/>
+      <c r="D1" s="197"/>
       <c r="E1" s="61"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2070,12 +2072,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
-      <c r="B3" s="193" t="s">
+      <c r="B3" s="198" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="193"/>
-      <c r="D3" s="193"/>
-      <c r="E3" s="194"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="199"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
@@ -2093,7 +2095,7 @@
         <v>55</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="62" t="s">
@@ -2113,49 +2115,49 @@
       <c r="E6" s="20"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="189" t="s">
-        <v>156</v>
-      </c>
-      <c r="C8" s="189"/>
+      <c r="B8" s="196" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="196"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="189"/>
-      <c r="C9" s="189"/>
+      <c r="B9" s="196"/>
+      <c r="C9" s="196"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="189"/>
-      <c r="C10" s="189"/>
+      <c r="B10" s="196"/>
+      <c r="C10" s="196"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="195" t="s">
+      <c r="A13" s="200" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="195"/>
-      <c r="C13" s="195"/>
-      <c r="D13" s="195"/>
-      <c r="E13" s="195"/>
+      <c r="B13" s="200"/>
+      <c r="C13" s="200"/>
+      <c r="D13" s="200"/>
+      <c r="E13" s="200"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="195"/>
-      <c r="B14" s="195"/>
-      <c r="C14" s="195"/>
-      <c r="D14" s="195"/>
-      <c r="E14" s="195"/>
+      <c r="A14" s="200"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="200"/>
+      <c r="D14" s="200"/>
+      <c r="E14" s="200"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="195"/>
-      <c r="B15" s="195"/>
-      <c r="C15" s="195"/>
-      <c r="D15" s="195"/>
-      <c r="E15" s="195"/>
+      <c r="A15" s="200"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="200"/>
+      <c r="E15" s="200"/>
     </row>
     <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="195"/>
-      <c r="B16" s="195"/>
-      <c r="C16" s="195"/>
-      <c r="D16" s="195"/>
-      <c r="E16" s="195"/>
+      <c r="A16" s="200"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="200"/>
+      <c r="E16" s="200"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
@@ -2181,13 +2183,13 @@
       <c r="E21" s="33"/>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="190" t="s">
+      <c r="A22" s="191" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="191"/>
+      <c r="B22" s="192"/>
       <c r="C22" s="5"/>
       <c r="D22" s="161">
-        <v>1066547.7</v>
+        <v>1719538.75</v>
       </c>
       <c r="E22" s="5"/>
     </row>
@@ -2198,7 +2200,7 @@
       <c r="B23" s="114"/>
       <c r="C23" s="5"/>
       <c r="D23" s="161">
-        <v>-263970.56</v>
+        <v>-425585.84</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -2209,7 +2211,7 @@
       <c r="B24" s="114"/>
       <c r="C24" s="5"/>
       <c r="D24" s="161">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="E24" s="5"/>
     </row>
@@ -2221,7 +2223,7 @@
       <c r="C25" s="54"/>
       <c r="D25" s="162">
         <f>SUM(D22:D24)</f>
-        <v>802577.99999999988</v>
+        <v>1293953</v>
       </c>
       <c r="E25" s="102"/>
       <c r="G25" s="21"/>
@@ -2286,7 +2288,7 @@
       <c r="D32" s="165"/>
       <c r="E32" s="103">
         <f>D25+D31</f>
-        <v>802577.99999999988</v>
+        <v>1293953</v>
       </c>
       <c r="F32" s="21"/>
     </row>
@@ -2300,29 +2302,29 @@
       <c r="E33" s="104"/>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="196" t="s">
+      <c r="A34" s="187" t="s">
         <v>137</v>
       </c>
-      <c r="B34" s="197"/>
+      <c r="B34" s="188"/>
       <c r="C34" s="51"/>
-      <c r="D34" s="161">
+      <c r="D34" s="232">
         <v>45000</v>
       </c>
-      <c r="E34" s="105" t="s">
-        <v>169</v>
+      <c r="E34" s="146" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="196" t="s">
-        <v>171</v>
-      </c>
-      <c r="B35" s="197"/>
+      <c r="A35" s="187" t="s">
+        <v>174</v>
+      </c>
+      <c r="B35" s="188"/>
       <c r="C35" s="51"/>
-      <c r="D35" s="187">
-        <v>380000</v>
+      <c r="D35" s="229">
+        <v>190000</v>
       </c>
       <c r="E35" s="105" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2334,7 +2336,7 @@
       <c r="D36" s="167"/>
       <c r="E36" s="106">
         <f>SUM(D34:D35)</f>
-        <v>425000</v>
+        <v>235000</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -2347,10 +2349,10 @@
       <c r="E37" s="107"/>
     </row>
     <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="190" t="s">
+      <c r="A38" s="191" t="s">
         <v>150</v>
       </c>
-      <c r="B38" s="191"/>
+      <c r="B38" s="192"/>
       <c r="C38" s="52"/>
       <c r="D38" s="169">
         <v>161303</v>
@@ -2360,10 +2362,10 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="190" t="s">
-        <v>173</v>
-      </c>
-      <c r="B39" s="191"/>
+      <c r="A39" s="191" t="s">
+        <v>164</v>
+      </c>
+      <c r="B39" s="192"/>
       <c r="C39" s="52"/>
       <c r="D39" s="170">
         <v>199876.87</v>
@@ -2399,40 +2401,40 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="51"/>
-      <c r="D42" s="188">
-        <v>624914.22</v>
+      <c r="D42" s="231">
+        <v>641714.36</v>
       </c>
       <c r="E42" s="115" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G42" s="89"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>110</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="172">
-        <v>46741.68</v>
+      <c r="D43" s="230">
+        <v>47994.65</v>
       </c>
       <c r="E43" s="115" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
         <f>A43</f>
-        <v>Sindicatos mes de MAYO</v>
+        <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="172">
-        <v>89132.76</v>
+      <c r="D44" s="230">
+        <v>91806.61</v>
       </c>
       <c r="E44" s="116" t="str">
         <f>E43</f>
@@ -2442,14 +2444,14 @@
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="str">
         <f>A44</f>
-        <v>Sindicatos mes de MAYO</v>
+        <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>111</v>
       </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="172">
-        <v>5193.5200000000004</v>
+      <c r="D45" s="230">
+        <v>5332.74</v>
       </c>
       <c r="E45" s="117" t="str">
         <f>E43</f>
@@ -2465,7 +2467,7 @@
       <c r="D46" s="173"/>
       <c r="E46" s="108">
         <f>SUM(D42:D45)</f>
-        <v>765982.18</v>
+        <v>786848.36</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2483,11 +2485,11 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="172">
-        <v>305642.36</v>
+      <c r="D48" s="230">
+        <v>413737.24</v>
       </c>
       <c r="E48" s="115" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2496,11 +2498,11 @@
       </c>
       <c r="B49" s="180"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="172">
-        <v>18758.310000000001</v>
+      <c r="D49" s="230">
+        <v>17281.75</v>
       </c>
       <c r="E49" s="115" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2509,11 +2511,11 @@
       </c>
       <c r="B50" s="114"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="172">
-        <v>999748.85</v>
+      <c r="D50" s="230">
+        <v>1033943.24</v>
       </c>
       <c r="E50" s="115" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2525,7 +2527,7 @@
       <c r="D51" s="174"/>
       <c r="E51" s="108">
         <f>SUM(D48:D50)</f>
-        <v>1324149.52</v>
+        <v>1464962.23</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2543,16 +2545,16 @@
       </c>
       <c r="B53" s="114"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="172">
+      <c r="D53" s="230">
         <v>189500</v>
       </c>
       <c r="E53" s="146" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="118" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B54" s="114"/>
       <c r="C54" s="5"/>
@@ -2560,7 +2562,7 @@
         <v>191400</v>
       </c>
       <c r="E54" s="146" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2573,7 +2575,7 @@
         <v>31400</v>
       </c>
       <c r="E55" s="146" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F55" s="42">
         <f>D54+D55+D56+D57</f>
@@ -2582,7 +2584,7 @@
     </row>
     <row r="56" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="118" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B56" s="114"/>
       <c r="C56" s="5"/>
@@ -2590,7 +2592,7 @@
         <v>46200</v>
       </c>
       <c r="E56" s="146" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F56" s="42">
         <f>F55-D54</f>
@@ -2607,33 +2609,33 @@
         <v>31400</v>
       </c>
       <c r="E57" s="146" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="190" t="s">
-        <v>163</v>
-      </c>
-      <c r="B58" s="191"/>
+      <c r="A58" s="191" t="s">
+        <v>159</v>
+      </c>
+      <c r="B58" s="192"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="172">
+      <c r="D58" s="230">
         <v>847000</v>
       </c>
       <c r="E58" s="146" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="190" t="s">
-        <v>168</v>
-      </c>
-      <c r="B59" s="191"/>
+      <c r="A59" s="191" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" s="192"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="172">
-        <v>120000</v>
+      <c r="D59" s="230">
+        <v>847000</v>
       </c>
       <c r="E59" s="146" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2646,27 +2648,27 @@
         <v>60000</v>
       </c>
       <c r="E60" s="146" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="196" t="s">
-        <v>175</v>
-      </c>
-      <c r="B61" s="197"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="187" t="s">
+        <v>179</v>
+      </c>
+      <c r="B61" s="188"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="172">
-        <v>65000</v>
+      <c r="D61" s="230">
+        <v>166200</v>
       </c>
       <c r="E61" s="146" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="190" t="s">
-        <v>161</v>
-      </c>
-      <c r="B62" s="191"/>
+      <c r="A62" s="191" t="s">
+        <v>158</v>
+      </c>
+      <c r="B62" s="192"/>
       <c r="C62" s="5"/>
       <c r="D62" s="172">
         <v>19500</v>
@@ -2684,7 +2686,7 @@
       <c r="D63" s="33"/>
       <c r="E63" s="112">
         <f>SUM(D53:D62)</f>
-        <v>1601400</v>
+        <v>2429600</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2761,7 +2763,7 @@
       <c r="D71" s="80"/>
       <c r="E71" s="81">
         <f>(SUM(E28:E69))</f>
-        <v>5430895.8100000005</v>
+        <v>6722149.7000000002</v>
       </c>
       <c r="F71" s="101"/>
       <c r="G71" s="42"/>
@@ -2795,22 +2797,22 @@
       <c r="E74" s="83"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="190"/>
-      <c r="B75" s="191"/>
+      <c r="A75" s="191"/>
+      <c r="B75" s="192"/>
       <c r="C75" s="5"/>
       <c r="D75" s="93"/>
       <c r="E75" s="69"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="190"/>
-      <c r="B76" s="191"/>
+      <c r="A76" s="191"/>
+      <c r="B76" s="192"/>
       <c r="C76" s="5"/>
       <c r="D76" s="71"/>
       <c r="E76" s="69"/>
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="196"/>
-      <c r="B77" s="197"/>
+      <c r="A77" s="187"/>
+      <c r="B77" s="188"/>
       <c r="C77" s="5"/>
       <c r="D77" s="71"/>
       <c r="E77" s="69"/>
@@ -2865,7 +2867,7 @@
       </c>
       <c r="B86" s="66">
         <f>E71</f>
-        <v>5430895.8100000005</v>
+        <v>6722149.7000000002</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2874,7 +2876,7 @@
       </c>
       <c r="B87" s="66">
         <f>E71-E69</f>
-        <v>5430895.8100000005</v>
+        <v>6722149.7000000002</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2898,25 +2900,25 @@
     <row r="90" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="91" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="198"/>
-      <c r="B92" s="198"/>
-      <c r="C92" s="198"/>
-      <c r="D92" s="198"/>
-      <c r="E92" s="198"/>
+      <c r="A92" s="189"/>
+      <c r="B92" s="189"/>
+      <c r="C92" s="189"/>
+      <c r="D92" s="189"/>
+      <c r="E92" s="189"/>
     </row>
     <row r="93" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="198"/>
-      <c r="B93" s="198"/>
-      <c r="C93" s="198"/>
-      <c r="D93" s="198"/>
-      <c r="E93" s="198"/>
+      <c r="A93" s="189"/>
+      <c r="B93" s="189"/>
+      <c r="C93" s="189"/>
+      <c r="D93" s="189"/>
+      <c r="E93" s="189"/>
     </row>
     <row r="94" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="198"/>
-      <c r="B94" s="198"/>
-      <c r="C94" s="198"/>
-      <c r="D94" s="198"/>
-      <c r="E94" s="198"/>
+      <c r="A94" s="189"/>
+      <c r="B94" s="189"/>
+      <c r="C94" s="189"/>
+      <c r="D94" s="189"/>
+      <c r="E94" s="189"/>
     </row>
     <row r="96" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="22"/>
@@ -2975,7 +2977,7 @@
       </c>
       <c r="B103" s="46">
         <f>-B87</f>
-        <v>-5430895.8100000005</v>
+        <v>-6722149.7000000002</v>
       </c>
       <c r="C103" s="23"/>
     </row>
@@ -2995,7 +2997,7 @@
       </c>
       <c r="B105" s="56">
         <f>SUM(B97:B104)</f>
-        <v>-1756625.9699999997</v>
+        <v>-3047879.8599999994</v>
       </c>
       <c r="C105" s="26"/>
       <c r="D105" s="42"/>
@@ -3033,7 +3035,7 @@
       </c>
       <c r="B110" s="160">
         <f>-B87</f>
-        <v>-5430895.8100000005</v>
+        <v>-6722149.7000000002</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -3055,7 +3057,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="52" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B113" s="160">
         <v>-3949</v>
@@ -3063,7 +3065,7 @@
     </row>
     <row r="114" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="52" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B114" s="186">
         <v>119941</v>
@@ -3093,7 +3095,7 @@
       </c>
       <c r="B117" s="98">
         <f>SUM(B109:C116)</f>
-        <v>4130734.6900000004</v>
+        <v>2839480.8000000007</v>
       </c>
       <c r="D117" s="42"/>
       <c r="E117" s="42"/>
@@ -3107,22 +3109,22 @@
       <c r="B119" s="96"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="200" t="s">
-        <v>178</v>
-      </c>
-      <c r="B120" s="200"/>
+      <c r="A120" s="193" t="s">
+        <v>168</v>
+      </c>
+      <c r="B120" s="193"/>
     </row>
     <row r="121" spans="1:5" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="201"/>
-      <c r="B121" s="201"/>
+      <c r="A121" s="194"/>
+      <c r="B121" s="194"/>
     </row>
     <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="201"/>
-      <c r="B122" s="201"/>
+      <c r="A122" s="194"/>
+      <c r="B122" s="194"/>
     </row>
     <row r="123" spans="1:5" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="202"/>
-      <c r="B123" s="202"/>
+      <c r="A123" s="195"/>
+      <c r="B123" s="195"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="96"/>
@@ -3138,16 +3140,16 @@
     </row>
     <row r="127" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="199" t="s">
+      <c r="A128" s="190" t="s">
         <v>30</v>
       </c>
-      <c r="B128" s="199"/>
-      <c r="C128" s="199"/>
+      <c r="B128" s="190"/>
+      <c r="C128" s="190"/>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A129" s="199"/>
-      <c r="B129" s="199"/>
-      <c r="C129" s="199"/>
+      <c r="A129" s="190"/>
+      <c r="B129" s="190"/>
+      <c r="C129" s="190"/>
     </row>
     <row r="130" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="85"/>
@@ -3179,35 +3181,40 @@
       <c r="M133" s="7"/>
     </row>
     <row r="134" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="198"/>
-      <c r="B134" s="198"/>
-      <c r="C134" s="198"/>
-      <c r="D134" s="198"/>
-      <c r="E134" s="198"/>
+      <c r="A134" s="189"/>
+      <c r="B134" s="189"/>
+      <c r="C134" s="189"/>
+      <c r="D134" s="189"/>
+      <c r="E134" s="189"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A135" s="198"/>
-      <c r="B135" s="198"/>
-      <c r="C135" s="198"/>
-      <c r="D135" s="198"/>
-      <c r="E135" s="198"/>
+      <c r="A135" s="189"/>
+      <c r="B135" s="189"/>
+      <c r="C135" s="189"/>
+      <c r="D135" s="189"/>
+      <c r="E135" s="189"/>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A136" s="198"/>
-      <c r="B136" s="198"/>
-      <c r="C136" s="198"/>
-      <c r="D136" s="198"/>
-      <c r="E136" s="198"/>
+      <c r="A136" s="189"/>
+      <c r="B136" s="189"/>
+      <c r="C136" s="189"/>
+      <c r="D136" s="189"/>
+      <c r="E136" s="189"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A137" s="198"/>
-      <c r="B137" s="198"/>
-      <c r="C137" s="198"/>
-      <c r="D137" s="198"/>
-      <c r="E137" s="198"/>
+      <c r="A137" s="189"/>
+      <c r="B137" s="189"/>
+      <c r="C137" s="189"/>
+      <c r="D137" s="189"/>
+      <c r="E137" s="189"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A134:E137"/>
     <mergeCell ref="A128:C129"/>
@@ -3223,11 +3230,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A120:B123"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="110" orientation="portrait" r:id="rId1"/>
@@ -3263,14 +3265,14 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="210"/>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
+      <c r="G1" s="202"/>
+      <c r="H1" s="202"/>
+      <c r="I1" s="202"/>
+      <c r="J1" s="202"/>
+      <c r="K1" s="202"/>
+      <c r="L1" s="202"/>
       <c r="M1" s="6"/>
     </row>
     <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -3313,110 +3315,110 @@
       <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="217" t="s">
+      <c r="A4" s="210" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="218"/>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
-      <c r="E4" s="218"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="218"/>
-      <c r="H4" s="218"/>
-      <c r="I4" s="218"/>
-      <c r="J4" s="218"/>
-      <c r="K4" s="218"/>
-      <c r="L4" s="218"/>
-      <c r="M4" s="219"/>
+      <c r="B4" s="211"/>
+      <c r="C4" s="211"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
+      <c r="M4" s="212"/>
     </row>
     <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="220"/>
-      <c r="B5" s="189"/>
-      <c r="C5" s="189"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
-      <c r="H5" s="189"/>
-      <c r="I5" s="189"/>
-      <c r="J5" s="189"/>
-      <c r="K5" s="189"/>
-      <c r="L5" s="189"/>
-      <c r="M5" s="221"/>
+      <c r="A5" s="213"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="196"/>
+      <c r="E5" s="196"/>
+      <c r="F5" s="196"/>
+      <c r="G5" s="196"/>
+      <c r="H5" s="196"/>
+      <c r="I5" s="196"/>
+      <c r="J5" s="196"/>
+      <c r="K5" s="196"/>
+      <c r="L5" s="196"/>
+      <c r="M5" s="214"/>
     </row>
     <row r="6" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="222"/>
-      <c r="B6" s="223"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="223"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="223"/>
-      <c r="H6" s="223"/>
-      <c r="I6" s="223"/>
-      <c r="J6" s="223"/>
-      <c r="K6" s="223"/>
-      <c r="L6" s="223"/>
-      <c r="M6" s="224"/>
+      <c r="A6" s="215"/>
+      <c r="B6" s="216"/>
+      <c r="C6" s="216"/>
+      <c r="D6" s="216"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="216"/>
+      <c r="H6" s="216"/>
+      <c r="I6" s="216"/>
+      <c r="J6" s="216"/>
+      <c r="K6" s="216"/>
+      <c r="L6" s="216"/>
+      <c r="M6" s="217"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="203" t="s">
+      <c r="A7" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="203" t="s">
+      <c r="B7" s="205" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="203" t="s">
+      <c r="C7" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="203" t="s">
+      <c r="D7" s="205" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="203" t="s">
+      <c r="E7" s="205" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="211" t="s">
+      <c r="F7" s="203" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="203" t="s">
+      <c r="G7" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="213" t="s">
+      <c r="H7" s="206" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="211" t="s">
+      <c r="I7" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="211" t="s">
+      <c r="J7" s="203" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="215" t="s">
+      <c r="K7" s="208" t="s">
         <v>59</v>
       </c>
       <c r="L7" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="209" t="s">
+      <c r="M7" s="201" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="203"/>
-      <c r="B8" s="204"/>
-      <c r="C8" s="203"/>
-      <c r="D8" s="204"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="212"/>
-      <c r="G8" s="203"/>
-      <c r="H8" s="214"/>
-      <c r="I8" s="212"/>
-      <c r="J8" s="212"/>
-      <c r="K8" s="216"/>
+      <c r="A8" s="205"/>
+      <c r="B8" s="218"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="218"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="204"/>
+      <c r="G8" s="205"/>
+      <c r="H8" s="207"/>
+      <c r="I8" s="204"/>
+      <c r="J8" s="204"/>
+      <c r="K8" s="209"/>
       <c r="L8" s="58" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 18/06</v>
-      </c>
-      <c r="M8" s="209"/>
+        <v>VTO 17/07</v>
+      </c>
+      <c r="M8" s="201"/>
     </row>
     <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="122">
@@ -3588,7 +3590,7 @@
         <v>63</v>
       </c>
       <c r="C12" s="130" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D12" s="130"/>
       <c r="E12" s="144">
@@ -4671,10 +4673,10 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="205" t="s">
+      <c r="A33" s="219" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="206"/>
+      <c r="B33" s="220"/>
       <c r="C33" s="137" t="s">
         <v>103</v>
       </c>
@@ -4719,11 +4721,11 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="207" t="s">
+      <c r="A34" s="221" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="207"/>
-      <c r="C34" s="208"/>
+      <c r="B34" s="221"/>
+      <c r="C34" s="222"/>
       <c r="D34" s="139"/>
       <c r="E34" s="147">
         <f>SUM(E9:E33)</f>
@@ -4768,82 +4770,90 @@
     </row>
     <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="198" t="str">
+      <c r="C37" s="189" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D37" s="198"/>
-      <c r="E37" s="198"/>
-      <c r="F37" s="198"/>
-      <c r="G37" s="198"/>
-      <c r="H37" s="198"/>
-      <c r="I37" s="198"/>
-      <c r="J37" s="198"/>
-      <c r="K37" s="198"/>
-      <c r="L37" s="198"/>
+      <c r="D37" s="189"/>
+      <c r="E37" s="189"/>
+      <c r="F37" s="189"/>
+      <c r="G37" s="189"/>
+      <c r="H37" s="189"/>
+      <c r="I37" s="189"/>
+      <c r="J37" s="189"/>
+      <c r="K37" s="189"/>
+      <c r="L37" s="189"/>
     </row>
     <row r="38" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="198"/>
-      <c r="D38" s="198"/>
-      <c r="E38" s="198"/>
-      <c r="F38" s="198"/>
-      <c r="G38" s="198"/>
-      <c r="H38" s="198"/>
-      <c r="I38" s="198"/>
-      <c r="J38" s="198"/>
-      <c r="K38" s="198"/>
-      <c r="L38" s="198"/>
+      <c r="C38" s="189"/>
+      <c r="D38" s="189"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="189"/>
+      <c r="G38" s="189"/>
+      <c r="H38" s="189"/>
+      <c r="I38" s="189"/>
+      <c r="J38" s="189"/>
+      <c r="K38" s="189"/>
+      <c r="L38" s="189"/>
     </row>
     <row r="39" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="198"/>
-      <c r="D39" s="198"/>
-      <c r="E39" s="198"/>
-      <c r="F39" s="198"/>
-      <c r="G39" s="198"/>
-      <c r="H39" s="198"/>
-      <c r="I39" s="198"/>
-      <c r="J39" s="198"/>
-      <c r="K39" s="198"/>
-      <c r="L39" s="198"/>
+      <c r="C39" s="189"/>
+      <c r="D39" s="189"/>
+      <c r="E39" s="189"/>
+      <c r="F39" s="189"/>
+      <c r="G39" s="189"/>
+      <c r="H39" s="189"/>
+      <c r="I39" s="189"/>
+      <c r="J39" s="189"/>
+      <c r="K39" s="189"/>
+      <c r="L39" s="189"/>
     </row>
     <row r="40" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="198"/>
-      <c r="D40" s="198"/>
-      <c r="E40" s="198"/>
-      <c r="F40" s="198"/>
-      <c r="G40" s="198"/>
-      <c r="H40" s="198"/>
-      <c r="I40" s="198"/>
-      <c r="J40" s="198"/>
-      <c r="K40" s="198"/>
-      <c r="L40" s="198"/>
+      <c r="C40" s="189"/>
+      <c r="D40" s="189"/>
+      <c r="E40" s="189"/>
+      <c r="F40" s="189"/>
+      <c r="G40" s="189"/>
+      <c r="H40" s="189"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="189"/>
+      <c r="K40" s="189"/>
+      <c r="L40" s="189"/>
     </row>
     <row r="41" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="198"/>
-      <c r="D41" s="198"/>
-      <c r="E41" s="198"/>
-      <c r="F41" s="198"/>
-      <c r="G41" s="198"/>
-      <c r="H41" s="198"/>
-      <c r="I41" s="198"/>
-      <c r="J41" s="198"/>
-      <c r="K41" s="198"/>
-      <c r="L41" s="198"/>
+      <c r="C41" s="189"/>
+      <c r="D41" s="189"/>
+      <c r="E41" s="189"/>
+      <c r="F41" s="189"/>
+      <c r="G41" s="189"/>
+      <c r="H41" s="189"/>
+      <c r="I41" s="189"/>
+      <c r="J41" s="189"/>
+      <c r="K41" s="189"/>
+      <c r="L41" s="189"/>
     </row>
     <row r="42" spans="1:15" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="198"/>
-      <c r="D42" s="198"/>
-      <c r="E42" s="198"/>
-      <c r="F42" s="198"/>
-      <c r="G42" s="198"/>
-      <c r="H42" s="198"/>
-      <c r="I42" s="198"/>
-      <c r="J42" s="198"/>
-      <c r="K42" s="198"/>
-      <c r="L42" s="198"/>
+      <c r="C42" s="189"/>
+      <c r="D42" s="189"/>
+      <c r="E42" s="189"/>
+      <c r="F42" s="189"/>
+      <c r="G42" s="189"/>
+      <c r="H42" s="189"/>
+      <c r="I42" s="189"/>
+      <c r="J42" s="189"/>
+      <c r="K42" s="189"/>
+      <c r="L42" s="189"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C37:L42"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="E1:L1"/>
     <mergeCell ref="I7:I8"/>
@@ -4853,14 +4863,6 @@
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="A4:M6"/>
-    <mergeCell ref="C37:L42"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4895,36 +4897,36 @@
       <c r="G5" s="177"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="225"/>
-      <c r="C6" s="226"/>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="227"/>
+      <c r="B6" s="223"/>
+      <c r="C6" s="224"/>
+      <c r="D6" s="224"/>
+      <c r="E6" s="224"/>
+      <c r="F6" s="224"/>
+      <c r="G6" s="225"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="225"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
-      <c r="G7" s="227"/>
+      <c r="B7" s="223"/>
+      <c r="C7" s="224"/>
+      <c r="D7" s="224"/>
+      <c r="E7" s="224"/>
+      <c r="F7" s="224"/>
+      <c r="G7" s="225"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="225"/>
-      <c r="C8" s="226"/>
-      <c r="D8" s="226"/>
-      <c r="E8" s="226"/>
-      <c r="F8" s="226"/>
-      <c r="G8" s="227"/>
+      <c r="B8" s="223"/>
+      <c r="C8" s="224"/>
+      <c r="D8" s="224"/>
+      <c r="E8" s="224"/>
+      <c r="F8" s="224"/>
+      <c r="G8" s="225"/>
     </row>
     <row r="9" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="228"/>
-      <c r="C9" s="229"/>
-      <c r="D9" s="229"/>
-      <c r="E9" s="229"/>
-      <c r="F9" s="229"/>
-      <c r="G9" s="230"/>
+      <c r="B9" s="226"/>
+      <c r="C9" s="227"/>
+      <c r="D9" s="227"/>
+      <c r="E9" s="227"/>
+      <c r="F9" s="227"/>
+      <c r="G9" s="228"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/2026/ANATOLE FRANCE/Junio/ANATOLE-Junio.xlsx
+++ b/2026/ANATOLE FRANCE/Junio/ANATOLE-Junio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDD8CEC-8002-48D2-9022-F23A22EE0068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CA83E1-883C-4A72-87DA-60C3BBD807FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$M$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$133</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$125</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="168">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -376,15 +381,9 @@
     <t>Redondeo</t>
   </si>
   <si>
-    <t>Alquiler Porteria</t>
-  </si>
-  <si>
     <t>Laura</t>
   </si>
   <si>
-    <t>German</t>
-  </si>
-  <si>
     <t>Hugo</t>
   </si>
   <si>
@@ -469,15 +468,6 @@
     <t xml:space="preserve">Nombre: </t>
   </si>
   <si>
-    <t>Cuello Natalia - Desobstruccion columna cocina 6B</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Desobstruccion columna cocina 1C</t>
-  </si>
-  <si>
-    <t>Transf 06/04</t>
-  </si>
-  <si>
     <t>Federacion Patronal - Seguro de consorcio</t>
   </si>
   <si>
@@ -496,21 +486,9 @@
     <t>Fracchia garcia Sebastian ezequiel</t>
   </si>
   <si>
-    <t>Cuello Natalia - Servicio de emergencia - Desobstruccion de colectora cloacal</t>
-  </si>
-  <si>
-    <t>Transf 22/05</t>
-  </si>
-  <si>
-    <t>Casa Ruan - Compra de materiales electricos</t>
-  </si>
-  <si>
     <t>Urbeco - Anticipo de cambio de tapa y marco en TQ cisterna de bombeo - Anticipo Reparacion e impermeabilizacion interna de respectiva cuba</t>
   </si>
   <si>
-    <t>Transf 14/05</t>
-  </si>
-  <si>
     <t>Transf 06/05</t>
   </si>
   <si>
@@ -520,24 +498,6 @@
     <t>Transf 12/05</t>
   </si>
   <si>
-    <t>Allianz Seguro - Seguro integral para consorcio</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Desobstruccion columna baño 4C</t>
-  </si>
-  <si>
-    <t>Transf 26/05</t>
-  </si>
-  <si>
-    <t>Punitorios mal cobrados 6C</t>
-  </si>
-  <si>
-    <t>El total del dinero en cuenta ($4.130.735) corresponde a CAJA EXTRAORDINARIA</t>
-  </si>
-  <si>
-    <t>Ingreso generado por expensas pagadas en cuenta bancaria erronea</t>
-  </si>
-  <si>
     <t>Barreiro Cristina</t>
   </si>
   <si>
@@ -565,10 +525,16 @@
     <t>Transf 02/06</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
-    <t>Transf 18/06</t>
+    <t>Inombiliaria Peduto - Honorarios (Sr. Vazquez Andres)</t>
+  </si>
+  <si>
+    <t>Transf 24/06</t>
+  </si>
+  <si>
+    <t>German Meilinger</t>
+  </si>
+  <si>
+    <t>El total del dinero en cuenta corresponde a CAJA EXTRAORDINARIA</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1241,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1423,10 +1389,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1518,7 +1480,6 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1538,8 +1499,26 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1553,12 +1532,6 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1568,20 +1541,23 @@
     <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1595,9 +1571,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1634,21 +1607,6 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1667,12 +1625,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1751,9 +1711,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1791,9 +1751,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1826,9 +1786,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1861,9 +1838,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2037,31 +2031,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M137"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M129"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="197" t="s">
+      <c r="B1" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
       <c r="E1" s="61"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="62" t="s">
         <v>26</v>
@@ -2070,16 +2064,16 @@
       <c r="D2" s="62"/>
       <c r="E2" s="63"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="187" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="199"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="187"/>
+      <c r="D3" s="187"/>
+      <c r="E3" s="188"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -2090,12 +2084,12 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="62" t="s">
@@ -2103,7 +2097,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>56</v>
       </c>
@@ -2114,57 +2108,57 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="196" t="s">
-        <v>171</v>
-      </c>
-      <c r="C8" s="196"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="196"/>
-      <c r="C9" s="196"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="196"/>
-      <c r="C10" s="196"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="200" t="s">
-        <v>136</v>
-      </c>
-      <c r="B13" s="200"/>
-      <c r="C13" s="200"/>
-      <c r="D13" s="200"/>
-      <c r="E13" s="200"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="200"/>
-      <c r="B14" s="200"/>
-      <c r="C14" s="200"/>
-      <c r="D14" s="200"/>
-      <c r="E14" s="200"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="200"/>
-      <c r="B15" s="200"/>
-      <c r="C15" s="200"/>
-      <c r="D15" s="200"/>
-      <c r="E15" s="200"/>
-    </row>
-    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="200"/>
-      <c r="B16" s="200"/>
-      <c r="C16" s="200"/>
-      <c r="D16" s="200"/>
-      <c r="E16" s="200"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="183" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="183"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="183"/>
+      <c r="C9" s="183"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="183"/>
+      <c r="C10" s="183"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="189" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="189"/>
+      <c r="C13" s="189"/>
+      <c r="D13" s="189"/>
+      <c r="E13" s="189"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="189"/>
+      <c r="B14" s="189"/>
+      <c r="C14" s="189"/>
+      <c r="D14" s="189"/>
+      <c r="E14" s="189"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="189"/>
+      <c r="B15" s="189"/>
+      <c r="C15" s="189"/>
+      <c r="D15" s="189"/>
+      <c r="E15" s="189"/>
+    </row>
+    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="189"/>
+      <c r="B16" s="189"/>
+      <c r="C16" s="189"/>
+      <c r="D16" s="189"/>
+      <c r="E16" s="189"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2173,7 +2167,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>31</v>
       </c>
@@ -2182,1054 +2176,949 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
     </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="191" t="s">
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="184" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="192"/>
+      <c r="B22" s="185"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="161">
+      <c r="D22" s="159">
         <v>1719538.75</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="70" t="s">
         <v>114</v>
       </c>
-      <c r="B23" s="114"/>
+      <c r="B23" s="112"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="161">
+      <c r="D23" s="159">
         <v>-425585.84</v>
       </c>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="B24" s="114"/>
+      <c r="B24" s="112"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="161">
+      <c r="D24" s="159">
         <v>0.09</v>
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="54" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="54"/>
       <c r="C25" s="54"/>
-      <c r="D25" s="162">
+      <c r="D25" s="160">
         <f>SUM(D22:D24)</f>
         <v>1293953</v>
       </c>
       <c r="E25" s="102"/>
       <c r="G25" s="21"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="161"/>
+      <c r="D26" s="159"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="161"/>
+      <c r="D27" s="159"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="161"/>
+      <c r="D28" s="159"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="163"/>
+      <c r="D29" s="161"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="163"/>
+      <c r="D30" s="161"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="54" t="s">
         <v>32</v>
       </c>
       <c r="B31" s="54"/>
       <c r="C31" s="54"/>
-      <c r="D31" s="164">
+      <c r="D31" s="162">
         <f>SUM(D26:D30)</f>
         <v>0</v>
       </c>
       <c r="E31" s="102"/>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="29" t="s">
         <v>1</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
-      <c r="D32" s="165"/>
+      <c r="D32" s="163"/>
       <c r="E32" s="103">
         <f>D25+D31</f>
         <v>1293953</v>
       </c>
       <c r="F32" s="21"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
-      <c r="D33" s="166"/>
+      <c r="D33" s="164"/>
       <c r="E33" s="104"/>
     </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="187" t="s">
-        <v>137</v>
-      </c>
-      <c r="B34" s="188"/>
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="190" t="s">
+        <v>135</v>
+      </c>
+      <c r="B34" s="191"/>
       <c r="C34" s="51"/>
-      <c r="D34" s="232">
+      <c r="D34" s="159">
         <v>45000</v>
       </c>
-      <c r="E34" s="146" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="187" t="s">
-        <v>174</v>
-      </c>
-      <c r="B35" s="188"/>
+      <c r="E34" s="225" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="190" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="191"/>
       <c r="C35" s="51"/>
-      <c r="D35" s="229">
+      <c r="D35" s="227">
         <v>190000</v>
       </c>
-      <c r="E35" s="105" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E35" s="226" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
         <v>15</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29"/>
-      <c r="D36" s="167"/>
-      <c r="E36" s="106">
+      <c r="D36" s="165"/>
+      <c r="E36" s="103">
         <f>SUM(D34:D35)</f>
         <v>235000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
         <v>29</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
-      <c r="D37" s="168"/>
-      <c r="E37" s="107"/>
-    </row>
-    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="191" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="192"/>
+      <c r="D37" s="166"/>
+      <c r="E37" s="105"/>
+    </row>
+    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="184" t="s">
+        <v>145</v>
+      </c>
+      <c r="B38" s="185"/>
       <c r="C38" s="52"/>
-      <c r="D38" s="169">
+      <c r="D38" s="167">
         <v>161303</v>
       </c>
-      <c r="E38" s="121" t="s">
+      <c r="E38" s="119" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="191" t="s">
-        <v>164</v>
-      </c>
-      <c r="B39" s="192"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="170">
-        <v>199876.87</v>
-      </c>
-      <c r="E39" s="121" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="29" t="s">
+    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="167"/>
-      <c r="E40" s="108">
-        <f>SUM(D38:D39)</f>
-        <v>361179.87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="34" t="s">
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="165"/>
+      <c r="E39" s="106">
+        <f>SUM(D38:D38)</f>
+        <v>161303</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="109"/>
-      <c r="C41" s="109"/>
-      <c r="D41" s="171"/>
-      <c r="E41" s="110"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="107"/>
+      <c r="C40" s="107"/>
+      <c r="D40" s="168"/>
+      <c r="E40" s="108"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="228">
+        <v>641714.36</v>
+      </c>
+      <c r="E41" s="113" t="s">
+        <v>152</v>
+      </c>
+      <c r="G41" s="89"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="231">
-        <v>641714.36</v>
-      </c>
-      <c r="E42" s="115" t="s">
-        <v>161</v>
-      </c>
-      <c r="G42" s="89"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>173</v>
+        <v>158</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="169">
+        <v>47994.65</v>
+      </c>
+      <c r="E42" s="113" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="str">
+        <f>A42</f>
+        <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="230">
-        <v>47994.65</v>
-      </c>
-      <c r="E43" s="115" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D43" s="169">
+        <v>91806.61</v>
+      </c>
+      <c r="E43" s="114" t="str">
+        <f>E42</f>
+        <v>Transf 12/05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="230">
-        <v>91806.61</v>
-      </c>
-      <c r="E44" s="116" t="str">
-        <f>E43</f>
+      <c r="D44" s="169">
+        <v>5332.74</v>
+      </c>
+      <c r="E44" s="115" t="str">
+        <f>E42</f>
         <v>Transf 12/05</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="str">
-        <f>A44</f>
-        <v>Sindicatos mes de JUNIO</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="230">
-        <v>5332.74</v>
-      </c>
-      <c r="E45" s="117" t="str">
-        <f>E43</f>
-        <v>Transf 12/05</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="29" t="s">
+    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="109"/>
-      <c r="C46" s="109"/>
-      <c r="D46" s="173"/>
-      <c r="E46" s="108">
-        <f>SUM(D42:D45)</f>
+      <c r="B45" s="107"/>
+      <c r="C45" s="107"/>
+      <c r="D45" s="170"/>
+      <c r="E45" s="106">
+        <f>SUM(D41:D44)</f>
         <v>786848.36</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="34" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="109"/>
-      <c r="C47" s="109"/>
-      <c r="D47" s="171"/>
-      <c r="E47" s="110"/>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
+      <c r="B46" s="107"/>
+      <c r="C46" s="107"/>
+      <c r="D46" s="168"/>
+      <c r="E46" s="108"/>
+    </row>
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B48" s="5"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="169">
+        <v>413737.24</v>
+      </c>
+      <c r="E47" s="113" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="176" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" s="177"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="230">
-        <v>413737.24</v>
-      </c>
-      <c r="E48" s="115" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="179" t="s">
-        <v>152</v>
-      </c>
-      <c r="B49" s="180"/>
+      <c r="D48" s="169">
+        <v>17281.75</v>
+      </c>
+      <c r="E48" s="113" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="70" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="112"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="230">
-        <v>17281.75</v>
-      </c>
-      <c r="E49" s="115" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="70" t="s">
-        <v>109</v>
-      </c>
-      <c r="B50" s="114"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="230">
+      <c r="D49" s="169">
         <v>1033943.24</v>
       </c>
-      <c r="E50" s="115" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="29" t="s">
+      <c r="E49" s="113" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="29" t="s">
         <v>4</v>
+      </c>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="171"/>
+      <c r="E50" s="106">
+        <f>SUM(D47:D49)</f>
+        <v>1464962.23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="34" t="s">
+        <v>146</v>
       </c>
       <c r="B51" s="29"/>
       <c r="C51" s="29"/>
-      <c r="D51" s="174"/>
-      <c r="E51" s="108">
-        <f>SUM(D48:D50)</f>
-        <v>1464962.23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="34" t="s">
+      <c r="D51" s="165"/>
+      <c r="E51" s="109"/>
+    </row>
+    <row r="52" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="112"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="169">
+        <v>189500</v>
+      </c>
+      <c r="E52" s="144" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="116" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" s="112"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="169">
+        <v>38400</v>
+      </c>
+      <c r="E53" s="144" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="184" t="s">
         <v>151</v>
       </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="167"/>
-      <c r="E52" s="111"/>
-    </row>
-    <row r="53" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="118" t="s">
-        <v>57</v>
-      </c>
-      <c r="B53" s="114"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="230">
-        <v>189500</v>
-      </c>
-      <c r="E53" s="146" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="118" t="s">
-        <v>156</v>
-      </c>
-      <c r="B54" s="114"/>
+      <c r="B54" s="185"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="172">
-        <v>191400</v>
-      </c>
-      <c r="E54" s="146" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="118" t="s">
-        <v>148</v>
-      </c>
-      <c r="B55" s="114"/>
+      <c r="D54" s="169">
+        <v>847000</v>
+      </c>
+      <c r="E54" s="144" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="184" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" s="185"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="172">
-        <v>31400</v>
-      </c>
-      <c r="E55" s="146" t="s">
+      <c r="D55" s="169">
+        <v>847000</v>
+      </c>
+      <c r="E55" s="144" t="s">
         <v>160</v>
       </c>
-      <c r="F55" s="42">
-        <f>D54+D55+D56+D57</f>
-        <v>300400</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="118" t="s">
+    </row>
+    <row r="56" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="116" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" s="112"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="169">
+        <v>60000</v>
+      </c>
+      <c r="E56" s="144" t="s">
         <v>165</v>
       </c>
-      <c r="B56" s="114"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="172">
-        <v>46200</v>
-      </c>
-      <c r="E56" s="146" t="s">
-        <v>160</v>
-      </c>
-      <c r="F56" s="42">
-        <f>F55-D54</f>
-        <v>109000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="118" t="s">
-        <v>147</v>
-      </c>
-      <c r="B57" s="114"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="172">
-        <v>31400</v>
-      </c>
-      <c r="E57" s="146" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="191" t="s">
-        <v>159</v>
-      </c>
-      <c r="B58" s="192"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="230">
-        <v>847000</v>
-      </c>
-      <c r="E58" s="146" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="191" t="s">
-        <v>176</v>
-      </c>
-      <c r="B59" s="192"/>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="34"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="110">
+        <f>SUM(D52:D56)</f>
+        <v>1981900</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="59"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="163"/>
+      <c r="E58" s="109"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="230">
-        <v>847000</v>
-      </c>
-      <c r="E59" s="146" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="118" t="s">
-        <v>138</v>
-      </c>
-      <c r="B60" s="114"/>
+      <c r="D59" s="169">
+        <v>69000</v>
+      </c>
+      <c r="E59" s="111"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B60" s="5"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="172">
-        <v>60000</v>
-      </c>
-      <c r="E60" s="146" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="187" t="s">
-        <v>179</v>
-      </c>
-      <c r="B61" s="188"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="230">
-        <v>166200</v>
-      </c>
-      <c r="E61" s="146" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="191" t="s">
-        <v>158</v>
-      </c>
-      <c r="B62" s="192"/>
+      <c r="D60" s="169">
+        <v>95455.99</v>
+      </c>
+      <c r="E60" s="39"/>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" s="50"/>
+      <c r="C61" s="50"/>
+      <c r="D61" s="74"/>
+      <c r="E61" s="68">
+        <f>SUM(D59:D60)</f>
+        <v>164455.99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="172">
-        <v>19500</v>
-      </c>
-      <c r="E62" s="146" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="29" t="s">
+      <c r="D62" s="67"/>
+      <c r="E62" s="75"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="76"/>
+      <c r="E63" s="77"/>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1"/>
+      <c r="D64" s="78"/>
+      <c r="E64" s="79"/>
+      <c r="F64" s="42"/>
+    </row>
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="80"/>
+      <c r="E65" s="81">
+        <f>(SUM(E28:E63))</f>
+        <v>6088422.5800000001</v>
+      </c>
+      <c r="F65" s="101"/>
+      <c r="G65" s="42"/>
+      <c r="H65" s="89"/>
+      <c r="I65" s="89"/>
+      <c r="J65" s="89"/>
+      <c r="K65" s="89"/>
+      <c r="L65" s="89"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D66" s="78"/>
+      <c r="E66" s="78"/>
+      <c r="H66" s="89"/>
+      <c r="I66" s="89"/>
+      <c r="J66" s="89"/>
+      <c r="K66" s="89"/>
+      <c r="L66" s="89"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D67" s="78"/>
+      <c r="E67" s="78"/>
+      <c r="H67" s="118"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="11"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="83"/>
+    </row>
+    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="184"/>
+      <c r="B69" s="185"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="93"/>
+      <c r="E69" s="69"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="184"/>
+      <c r="B70" s="185"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="71"/>
+      <c r="E70" s="69"/>
+    </row>
+    <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="190"/>
+      <c r="B71" s="191"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="71"/>
+      <c r="E71" s="69"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="70"/>
+      <c r="B72" s="72"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="71"/>
+      <c r="E72" s="69"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="48"/>
+      <c r="B73" s="47"/>
+      <c r="C73" s="47"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55">
+        <f>SUM(D69:D72)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="147" t="s">
+        <v>19</v>
+      </c>
+      <c r="B76" s="148"/>
+      <c r="C76" s="148"/>
+      <c r="D76" s="149"/>
+      <c r="E76" s="178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B78" s="9"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="60">
+        <f>E73+E76</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80" s="66">
+        <f>E65</f>
+        <v>6088422.5800000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" s="66">
+        <f>E65-E63</f>
+        <v>6088422.5800000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82" s="66">
+        <f>E78-E76</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B83" s="66">
+        <f>E78</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="192"/>
+      <c r="B86" s="192"/>
+      <c r="C86" s="192"/>
+      <c r="D86" s="192"/>
+      <c r="E86" s="192"/>
+    </row>
+    <row r="87" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="192"/>
+      <c r="B87" s="192"/>
+      <c r="C87" s="192"/>
+      <c r="D87" s="192"/>
+      <c r="E87" s="192"/>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="192"/>
+      <c r="B88" s="192"/>
+      <c r="C88" s="192"/>
+      <c r="D88" s="192"/>
+      <c r="E88" s="192"/>
+    </row>
+    <row r="90" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="22"/>
+      <c r="B90" s="90"/>
+      <c r="C90" s="23"/>
+    </row>
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="32"/>
+      <c r="B91" s="56">
+        <v>0</v>
+      </c>
+      <c r="C91" s="25"/>
+    </row>
+    <row r="92" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" s="39">
+        <f>PRORRATEO!G34</f>
+        <v>5515222.6900000013</v>
+      </c>
+      <c r="C92" s="23"/>
+    </row>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="24"/>
+      <c r="B93" s="39">
+        <v>0</v>
+      </c>
+      <c r="C93" s="23"/>
+    </row>
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B94" s="73">
+        <f>B124</f>
+        <v>0</v>
+      </c>
+      <c r="C94" s="23"/>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="27"/>
+      <c r="B95" s="46"/>
+      <c r="C95" s="23"/>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B96" s="46"/>
+      <c r="C96" s="23"/>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" s="46">
+        <f>-B81</f>
+        <v>-6088422.5800000001</v>
+      </c>
+      <c r="C97" s="23"/>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B98" s="46">
+        <f>-(B82)</f>
+        <v>0</v>
+      </c>
+      <c r="C98" s="23"/>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="B63" s="34"/>
-      <c r="C63" s="34"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="112">
-        <f>SUM(D53:D62)</f>
-        <v>2429600</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B64" s="59"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="165"/>
-      <c r="E64" s="111"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="172">
-        <v>69000</v>
-      </c>
-      <c r="E65" s="113"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="172">
-        <v>81606.240000000005</v>
-      </c>
-      <c r="E66" s="39"/>
-    </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" s="50"/>
-      <c r="C67" s="50"/>
-      <c r="D67" s="74"/>
-      <c r="E67" s="68">
-        <f>SUM(D65:D66)</f>
-        <v>150606.24</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="67"/>
-      <c r="E68" s="75"/>
-    </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="B69" s="30"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="76"/>
-      <c r="E69" s="77"/>
-    </row>
-    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="1"/>
-      <c r="D70" s="78"/>
-      <c r="E70" s="79"/>
-      <c r="F70" s="42"/>
-    </row>
-    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="80"/>
-      <c r="E71" s="81">
-        <f>(SUM(E28:E69))</f>
-        <v>6722149.7000000002</v>
-      </c>
-      <c r="F71" s="101"/>
-      <c r="G71" s="42"/>
-      <c r="H71" s="89"/>
-      <c r="I71" s="89"/>
-      <c r="J71" s="89"/>
-      <c r="K71" s="89"/>
-      <c r="L71" s="89"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D72" s="78"/>
-      <c r="E72" s="78"/>
-      <c r="H72" s="89"/>
-      <c r="I72" s="89"/>
-      <c r="J72" s="89"/>
-      <c r="K72" s="89"/>
-      <c r="L72" s="89"/>
-    </row>
-    <row r="73" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D73" s="78"/>
-      <c r="E73" s="78"/>
-      <c r="H73" s="120"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="11"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="82"/>
-      <c r="E74" s="83"/>
-    </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="191"/>
-      <c r="B75" s="192"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="93"/>
-      <c r="E75" s="69"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="191"/>
-      <c r="B76" s="192"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="71"/>
-      <c r="E76" s="69"/>
-    </row>
-    <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="187"/>
-      <c r="B77" s="188"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="71"/>
-      <c r="E77" s="69"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="70"/>
-      <c r="B78" s="72"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="71"/>
-      <c r="E78" s="69"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="48"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
-      <c r="D79" s="55"/>
-      <c r="E79" s="55">
-        <f>SUM(D75:D78)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="81" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="149" t="s">
-        <v>19</v>
-      </c>
-      <c r="B82" s="150"/>
-      <c r="C82" s="150"/>
-      <c r="D82" s="151"/>
-      <c r="E82" s="181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B84" s="9"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="60">
-        <f>E79+E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="65" t="s">
-        <v>13</v>
-      </c>
-      <c r="B86" s="66">
-        <f>E71</f>
-        <v>6722149.7000000002</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="65" t="s">
-        <v>14</v>
-      </c>
-      <c r="B87" s="66">
-        <f>E71-E69</f>
-        <v>6722149.7000000002</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="B88" s="66">
-        <f>E84-E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="65" t="s">
-        <v>37</v>
-      </c>
-      <c r="B89" s="66">
-        <f>E84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="189"/>
-      <c r="B92" s="189"/>
-      <c r="C92" s="189"/>
-      <c r="D92" s="189"/>
-      <c r="E92" s="189"/>
-    </row>
-    <row r="93" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="189"/>
-      <c r="B93" s="189"/>
-      <c r="C93" s="189"/>
-      <c r="D93" s="189"/>
-      <c r="E93" s="189"/>
-    </row>
-    <row r="94" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="189"/>
-      <c r="B94" s="189"/>
-      <c r="C94" s="189"/>
-      <c r="D94" s="189"/>
-      <c r="E94" s="189"/>
-    </row>
-    <row r="96" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="22"/>
-      <c r="B96" s="90"/>
-      <c r="C96" s="23"/>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="32"/>
-      <c r="B97" s="56">
-        <v>0</v>
-      </c>
-      <c r="C97" s="25"/>
-    </row>
-    <row r="98" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B98" s="39">
+      <c r="B99" s="56">
+        <f>SUM(B91:B98)</f>
+        <v>-573199.88999999873</v>
+      </c>
+      <c r="C99" s="26"/>
+      <c r="D99" s="42"/>
+    </row>
+    <row r="100" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="40"/>
+      <c r="C100" s="26"/>
+      <c r="D100" s="42"/>
+      <c r="E100" s="91"/>
+      <c r="F100" s="92"/>
+    </row>
+    <row r="101" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="41"/>
+      <c r="C101" s="26"/>
+    </row>
+    <row r="102" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102"/>
+      <c r="B102" s="40"/>
+      <c r="C102" s="36"/>
+    </row>
+    <row r="103" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="95" t="s">
+        <v>128</v>
+      </c>
+      <c r="B103" s="146">
+        <v>4130734.6900000004</v>
+      </c>
+      <c r="C103" s="36"/>
+      <c r="D103" s="45"/>
+      <c r="E103" s="42"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="B104" s="158">
+        <f>-B81</f>
+        <v>-6088422.5800000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B105" s="99">
+        <f>-B82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="B106" s="158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B107" s="99">
+        <f>B124</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="B108" s="100">
         <f>PRORRATEO!G34</f>
-        <v>3674269.8400000008</v>
-      </c>
-      <c r="C98" s="23"/>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="24"/>
-      <c r="B99" s="39">
-        <v>0</v>
-      </c>
-      <c r="C99" s="23"/>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B100" s="73">
-        <f>B132</f>
-        <v>0</v>
-      </c>
-      <c r="C100" s="23"/>
-    </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="27"/>
-      <c r="B101" s="46"/>
-      <c r="C101" s="23"/>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="B102" s="46"/>
-      <c r="C102" s="23"/>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B103" s="46">
-        <f>-B87</f>
-        <v>-6722149.7000000002</v>
-      </c>
-      <c r="C103" s="23"/>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B104" s="46">
-        <f>-(B88)</f>
-        <v>0</v>
-      </c>
-      <c r="C104" s="23"/>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B105" s="56">
-        <f>SUM(B97:B104)</f>
-        <v>-3047879.8599999994</v>
-      </c>
-      <c r="C105" s="26"/>
-      <c r="D105" s="42"/>
-    </row>
-    <row r="106" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B106" s="40"/>
-      <c r="C106" s="26"/>
-      <c r="D106" s="42"/>
-      <c r="E106" s="91"/>
-      <c r="F106" s="92"/>
-    </row>
-    <row r="107" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B107" s="41"/>
-      <c r="C107" s="26"/>
-    </row>
-    <row r="108" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108"/>
-      <c r="B108" s="40"/>
-      <c r="C108" s="36"/>
-    </row>
-    <row r="109" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="95" t="s">
-        <v>130</v>
-      </c>
-      <c r="B109" s="148">
-        <v>5421368.6600000001</v>
-      </c>
-      <c r="C109" s="36"/>
-      <c r="D109" s="45"/>
+        <v>5515222.6900000013</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="B109" s="98">
+        <f>SUM(B103:C108)</f>
+        <v>3557534.8000000017</v>
+      </c>
+      <c r="D109" s="42"/>
       <c r="E109" s="42"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="52" t="s">
-        <v>47</v>
-      </c>
-      <c r="B110" s="160">
-        <f>-B87</f>
-        <v>-6722149.7000000002</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B111" s="99">
-        <f>-B88</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="B112" s="99">
-        <v>350000</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="52" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="96"/>
+      <c r="B110" s="96"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="96"/>
+      <c r="B111" s="96"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="194" t="s">
         <v>167</v>
       </c>
-      <c r="B113" s="160">
-        <v>-3949</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B114" s="186">
-        <v>119941</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="B115" s="99">
-        <f>B132</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="B116" s="100">
-        <f>PRORRATEO!G34</f>
-        <v>3674269.8400000008</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="97" t="s">
-        <v>44</v>
-      </c>
-      <c r="B117" s="98">
-        <f>SUM(B109:C116)</f>
-        <v>2839480.8000000007</v>
-      </c>
-      <c r="D117" s="42"/>
-      <c r="E117" s="42"/>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B112" s="194"/>
+    </row>
+    <row r="113" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="195"/>
+      <c r="B113" s="195"/>
+    </row>
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="195"/>
+      <c r="B114" s="195"/>
+    </row>
+    <row r="115" spans="1:13" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="196"/>
+      <c r="B115" s="196"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="96"/>
+      <c r="B116" s="96"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="96"/>
+      <c r="B117" s="96"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="96"/>
       <c r="B118" s="96"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="96"/>
-      <c r="B119" s="96"/>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="193" t="s">
-        <v>168</v>
+        <v>30</v>
       </c>
       <c r="B120" s="193"/>
-    </row>
-    <row r="121" spans="1:5" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="194"/>
-      <c r="B121" s="194"/>
-    </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="194"/>
-      <c r="B122" s="194"/>
-    </row>
-    <row r="123" spans="1:5" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="195"/>
-      <c r="B123" s="195"/>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="96"/>
-      <c r="B124" s="96"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="96"/>
-      <c r="B125" s="96"/>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="96"/>
-      <c r="B126" s="96"/>
-    </row>
-    <row r="127" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="190" t="s">
-        <v>30</v>
-      </c>
-      <c r="B128" s="190"/>
-      <c r="C128" s="190"/>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A129" s="190"/>
-      <c r="B129" s="190"/>
-      <c r="C129" s="190"/>
-    </row>
-    <row r="130" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="85"/>
-      <c r="B130" s="35">
-        <v>0</v>
-      </c>
-      <c r="C130" s="35">
+      <c r="C120" s="193"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="193"/>
+      <c r="B121" s="193"/>
+      <c r="C121" s="193"/>
+    </row>
+    <row r="122" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="85"/>
+      <c r="B122" s="35">
+        <v>0</v>
+      </c>
+      <c r="C122" s="35">
         <v>40000</v>
       </c>
-      <c r="E130" s="101"/>
-    </row>
-    <row r="131" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="85"/>
-      <c r="B131" s="87"/>
-      <c r="C131" s="84"/>
-      <c r="D131" s="101"/>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A132" s="43" t="s">
+      <c r="E122" s="101"/>
+    </row>
+    <row r="123" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="85"/>
+      <c r="B123" s="87"/>
+      <c r="C123" s="84"/>
+      <c r="D123" s="101"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="B132" s="86">
-        <f>SUM(B130:B131)</f>
-        <v>0</v>
-      </c>
-      <c r="C132" s="44"/>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M133" s="7"/>
-    </row>
-    <row r="134" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="189"/>
-      <c r="B134" s="189"/>
-      <c r="C134" s="189"/>
-      <c r="D134" s="189"/>
-      <c r="E134" s="189"/>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A135" s="189"/>
-      <c r="B135" s="189"/>
-      <c r="C135" s="189"/>
-      <c r="D135" s="189"/>
-      <c r="E135" s="189"/>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A136" s="189"/>
-      <c r="B136" s="189"/>
-      <c r="C136" s="189"/>
-      <c r="D136" s="189"/>
-      <c r="E136" s="189"/>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A137" s="189"/>
-      <c r="B137" s="189"/>
-      <c r="C137" s="189"/>
-      <c r="D137" s="189"/>
-      <c r="E137" s="189"/>
+      <c r="B124" s="86">
+        <f>SUM(B122:B123)</f>
+        <v>0</v>
+      </c>
+      <c r="C124" s="44"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M125" s="7"/>
+    </row>
+    <row r="126" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="192"/>
+      <c r="B126" s="192"/>
+      <c r="C126" s="192"/>
+      <c r="D126" s="192"/>
+      <c r="E126" s="192"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" s="192"/>
+      <c r="B127" s="192"/>
+      <c r="C127" s="192"/>
+      <c r="D127" s="192"/>
+      <c r="E127" s="192"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="192"/>
+      <c r="B128" s="192"/>
+      <c r="C128" s="192"/>
+      <c r="D128" s="192"/>
+      <c r="E128" s="192"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="192"/>
+      <c r="B129" s="192"/>
+      <c r="C129" s="192"/>
+      <c r="D129" s="192"/>
+      <c r="E129" s="192"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="17">
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A126:E129"/>
+    <mergeCell ref="A120:C121"/>
+    <mergeCell ref="A86:E88"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A112:B115"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A134:E137"/>
-    <mergeCell ref="A128:C129"/>
-    <mergeCell ref="A92:E94"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A120:B123"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="110" orientation="portrait" r:id="rId1"/>
@@ -3240,42 +3129,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="204"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3284,7 +3173,7 @@
         <v>58</v>
       </c>
       <c r="F2" s="6"/>
-      <c r="G2" s="119">
+      <c r="G2" s="117">
         <v>0</v>
       </c>
       <c r="H2" s="6"/>
@@ -3292,14 +3181,14 @@
       <c r="J2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="152">
+      <c r="K2" s="150">
         <v>5430895.8100000005</v>
       </c>
       <c r="L2" s="94"/>
       <c r="M2" s="53"/>
       <c r="N2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3314,207 +3203,208 @@
       <c r="L3" s="57"/>
       <c r="M3" s="57"/>
     </row>
-    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="210" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="211"/>
-      <c r="C4" s="211"/>
-      <c r="D4" s="211"/>
-      <c r="E4" s="211"/>
-      <c r="F4" s="211"/>
-      <c r="G4" s="211"/>
-      <c r="H4" s="211"/>
-      <c r="I4" s="211"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="211"/>
-      <c r="L4" s="211"/>
-      <c r="M4" s="212"/>
-    </row>
-    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="213"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="196"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="196"/>
-      <c r="I5" s="196"/>
-      <c r="J5" s="196"/>
-      <c r="K5" s="196"/>
-      <c r="L5" s="196"/>
-      <c r="M5" s="214"/>
-    </row>
-    <row r="6" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="215"/>
-      <c r="B6" s="216"/>
-      <c r="C6" s="216"/>
-      <c r="D6" s="216"/>
-      <c r="E6" s="216"/>
-      <c r="F6" s="216"/>
-      <c r="G6" s="216"/>
-      <c r="H6" s="216"/>
-      <c r="I6" s="216"/>
-      <c r="J6" s="216"/>
-      <c r="K6" s="216"/>
-      <c r="L6" s="216"/>
-      <c r="M6" s="217"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="205" t="s">
+    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="211" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="212"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
+      <c r="M4" s="213"/>
+    </row>
+    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="214"/>
+      <c r="B5" s="183"/>
+      <c r="C5" s="183"/>
+      <c r="D5" s="183"/>
+      <c r="E5" s="183"/>
+      <c r="F5" s="183"/>
+      <c r="G5" s="183"/>
+      <c r="H5" s="183"/>
+      <c r="I5" s="183"/>
+      <c r="J5" s="183"/>
+      <c r="K5" s="183"/>
+      <c r="L5" s="183"/>
+      <c r="M5" s="215"/>
+    </row>
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="216"/>
+      <c r="B6" s="217"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="217"/>
+      <c r="E6" s="217"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="217"/>
+      <c r="H6" s="217"/>
+      <c r="I6" s="217"/>
+      <c r="J6" s="217"/>
+      <c r="K6" s="217"/>
+      <c r="L6" s="217"/>
+      <c r="M6" s="218"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="197" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="205" t="s">
+      <c r="B7" s="197" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="205" t="s">
+      <c r="C7" s="197" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="205" t="s">
+      <c r="D7" s="197" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="205" t="s">
+      <c r="E7" s="197" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="203" t="s">
+      <c r="F7" s="205" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="205" t="s">
+      <c r="G7" s="197" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="206" t="s">
+      <c r="H7" s="207" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="203" t="s">
+      <c r="I7" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="203" t="s">
+      <c r="J7" s="205" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="208" t="s">
+      <c r="K7" s="209" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="153" t="s">
+      <c r="L7" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="201" t="s">
+      <c r="M7" s="203" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="205"/>
-      <c r="B8" s="218"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="218"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="204"/>
-      <c r="G8" s="205"/>
-      <c r="H8" s="207"/>
-      <c r="I8" s="204"/>
-      <c r="J8" s="204"/>
-      <c r="K8" s="209"/>
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="197"/>
+      <c r="B8" s="198"/>
+      <c r="C8" s="197"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="197"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="197"/>
+      <c r="H8" s="208"/>
+      <c r="I8" s="206"/>
+      <c r="J8" s="206"/>
+      <c r="K8" s="210"/>
       <c r="L8" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="M8" s="201"/>
-    </row>
-    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="122">
+      <c r="M8" s="203"/>
+    </row>
+    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="120">
         <v>1</v>
       </c>
-      <c r="B9" s="122" t="s">
+      <c r="B9" s="120" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="122" t="s">
+      <c r="C9" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="122" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" s="144">
+      <c r="D9" s="120" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="142">
         <v>3.43</v>
       </c>
-      <c r="F9" s="124">
-        <v>135708.01</v>
-      </c>
-      <c r="G9" s="133">
-        <v>139780</v>
-      </c>
-      <c r="H9" s="125">
+      <c r="F9" s="122">
+        <v>182208.01</v>
+      </c>
+      <c r="G9" s="131">
+        <f>F9</f>
+        <v>182208.01</v>
+      </c>
+      <c r="H9" s="123">
         <f t="shared" ref="H9:H33" si="0">F9-G9</f>
-        <v>-4071.9899999999907</v>
-      </c>
-      <c r="I9" s="125">
+        <v>0</v>
+      </c>
+      <c r="I9" s="123">
         <f>IF(H9&gt;0,H9*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="126">
+      <c r="J9" s="124">
         <f>K$2*E9%</f>
         <v>186279.72628300005</v>
       </c>
-      <c r="K9" s="127">
+      <c r="K9" s="125">
         <f>G$2*E9/100</f>
         <v>0</v>
       </c>
-      <c r="L9" s="128">
+      <c r="L9" s="126">
         <f t="shared" ref="L9:L33" si="1">ROUND(SUM(H9:K9),0) + N9</f>
-        <v>182208.01</v>
-      </c>
-      <c r="M9" s="129">
+        <v>186280.01</v>
+      </c>
+      <c r="M9" s="127">
         <f t="shared" ref="M9:M33" si="2">ROUND(L9*3%,0) + L9</f>
-        <v>187674.01</v>
+        <v>191868.01</v>
       </c>
       <c r="N9" s="42">
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="131">
+    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="129">
         <f>A9+1</f>
         <v>2</v>
       </c>
-      <c r="B10" s="131" t="s">
+      <c r="B10" s="129" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="131" t="s">
+      <c r="C10" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="132" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" s="145">
+      <c r="D10" s="130" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" s="143">
         <v>2.95</v>
       </c>
-      <c r="F10" s="133">
-        <v>116717.02</v>
-      </c>
-      <c r="G10" s="133">
+      <c r="F10" s="131">
+        <v>160211.01999999999</v>
+      </c>
+      <c r="G10" s="131">
         <f>F10</f>
-        <v>116717.02</v>
-      </c>
-      <c r="H10" s="125">
+        <v>160211.01999999999</v>
+      </c>
+      <c r="H10" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="125">
+      <c r="I10" s="123">
         <f t="shared" ref="I10:I33" si="3">IF(H10&gt;0,H10*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="126">
+      <c r="J10" s="124">
         <f t="shared" ref="J10:J32" si="4">K$2*E10%</f>
         <v>160211.42639500002</v>
       </c>
-      <c r="K10" s="127">
+      <c r="K10" s="125">
         <f t="shared" ref="K10:K32" si="5">G$2*E10/100</f>
         <v>0</v>
       </c>
-      <c r="L10" s="128">
+      <c r="L10" s="126">
         <f t="shared" si="1"/>
         <v>160211.01999999999</v>
       </c>
-      <c r="M10" s="129">
+      <c r="M10" s="127">
         <f t="shared" si="2"/>
         <v>165017.01999999999</v>
       </c>
@@ -3524,52 +3414,52 @@
       </c>
       <c r="O10" s="42"/>
     </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="131">
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="129">
         <f t="shared" ref="A11:A32" si="6">A10+1</f>
         <v>3</v>
       </c>
-      <c r="B11" s="131" t="s">
+      <c r="B11" s="129" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="131" t="s">
+      <c r="C11" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="132" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="145">
+      <c r="D11" s="130" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" s="143">
         <f>5.78+1.02</f>
         <v>6.8000000000000007</v>
       </c>
-      <c r="F11" s="133">
-        <v>260971.03</v>
-      </c>
-      <c r="G11" s="133">
+      <c r="F11" s="131">
+        <v>369301.03</v>
+      </c>
+      <c r="G11" s="131">
         <f>F11</f>
-        <v>260971.03</v>
-      </c>
-      <c r="H11" s="125">
+        <v>369301.03</v>
+      </c>
+      <c r="H11" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="125">
+      <c r="I11" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J11" s="126">
+      <c r="J11" s="124">
         <f t="shared" si="4"/>
         <v>369300.91508000006</v>
       </c>
-      <c r="K11" s="127">
+      <c r="K11" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="128">
+      <c r="L11" s="126">
         <f t="shared" si="1"/>
         <v>369301.03</v>
       </c>
-      <c r="M11" s="129">
+      <c r="M11" s="127">
         <f t="shared" si="2"/>
         <v>380380.03</v>
       </c>
@@ -3578,53 +3468,54 @@
         <v>0.03</v>
       </c>
       <c r="O11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="122">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="120">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="B12" s="122" t="s">
+      <c r="B12" s="120" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="130" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" s="130"/>
-      <c r="E12" s="144">
+      <c r="C12" s="128" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="128"/>
+      <c r="E12" s="142">
         <v>3.43</v>
       </c>
-      <c r="F12" s="124">
-        <v>131759.04000000001</v>
-      </c>
-      <c r="G12" s="133">
-        <v>135712.04</v>
-      </c>
-      <c r="H12" s="125">
+      <c r="F12" s="122">
+        <v>182327.04000000001</v>
+      </c>
+      <c r="G12" s="131">
+        <f>F12</f>
+        <v>182327.04000000001</v>
+      </c>
+      <c r="H12" s="123">
         <f t="shared" si="0"/>
-        <v>-3953</v>
-      </c>
-      <c r="I12" s="125">
+        <v>0</v>
+      </c>
+      <c r="I12" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J12" s="126">
+      <c r="J12" s="124">
         <f t="shared" si="4"/>
         <v>186279.72628300005</v>
       </c>
-      <c r="K12" s="127">
+      <c r="K12" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L12" s="128">
+      <c r="L12" s="126">
         <f t="shared" si="1"/>
-        <v>182327.04000000001</v>
-      </c>
-      <c r="M12" s="129">
+        <v>186280.04</v>
+      </c>
+      <c r="M12" s="127">
         <f t="shared" si="2"/>
-        <v>187797.04</v>
+        <v>191868.04</v>
       </c>
       <c r="N12" s="42">
         <f t="shared" si="7"/>
@@ -3632,49 +3523,49 @@
       </c>
       <c r="P12" s="42"/>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="122">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="120">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="B13" s="122" t="s">
+      <c r="B13" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="122" t="s">
+      <c r="C13" s="120" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="130"/>
-      <c r="E13" s="144">
+      <c r="D13" s="128"/>
+      <c r="E13" s="142">
         <v>2.95</v>
       </c>
-      <c r="F13" s="124">
-        <v>116717.05</v>
-      </c>
-      <c r="G13" s="133">
+      <c r="F13" s="122">
+        <v>160211.04999999999</v>
+      </c>
+      <c r="G13" s="131">
         <f>F13</f>
-        <v>116717.05</v>
-      </c>
-      <c r="H13" s="125">
+        <v>160211.04999999999</v>
+      </c>
+      <c r="H13" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="125">
+      <c r="I13" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J13" s="126">
+      <c r="J13" s="124">
         <f t="shared" si="4"/>
         <v>160211.42639500002</v>
       </c>
-      <c r="K13" s="127">
+      <c r="K13" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L13" s="128">
+      <c r="L13" s="126">
         <f t="shared" si="1"/>
         <v>160211.04999999999</v>
       </c>
-      <c r="M13" s="129">
+      <c r="M13" s="127">
         <f t="shared" si="2"/>
         <v>165017.04999999999</v>
       </c>
@@ -3684,308 +3575,313 @@
       </c>
       <c r="P13" s="42"/>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="131">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="129">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="B14" s="131" t="s">
+      <c r="B14" s="129" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="131" t="s">
+      <c r="C14" s="129" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="131"/>
-      <c r="E14" s="144">
+      <c r="D14" s="129"/>
+      <c r="E14" s="142">
         <v>5.69</v>
       </c>
-      <c r="F14" s="124">
-        <v>225125.06</v>
-      </c>
-      <c r="G14" s="133">
-        <v>231879.06</v>
-      </c>
-      <c r="H14" s="125">
+      <c r="F14" s="122">
+        <v>302264.06</v>
+      </c>
+      <c r="G14" s="131">
+        <f>F14</f>
+        <v>302264.06</v>
+      </c>
+      <c r="H14" s="123">
         <f t="shared" si="0"/>
-        <v>-6754</v>
-      </c>
-      <c r="I14" s="125">
+        <v>0</v>
+      </c>
+      <c r="I14" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J14" s="126">
+      <c r="J14" s="124">
         <f t="shared" si="4"/>
         <v>309017.97158900008</v>
       </c>
-      <c r="K14" s="127">
+      <c r="K14" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L14" s="128">
+      <c r="L14" s="126">
         <f t="shared" si="1"/>
-        <v>302264.06</v>
-      </c>
-      <c r="M14" s="129">
+        <v>309018.06</v>
+      </c>
+      <c r="M14" s="127">
         <f t="shared" si="2"/>
-        <v>311332.06</v>
+        <v>318289.06</v>
       </c>
       <c r="N14" s="42">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
       <c r="O14" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="122">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="120">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="B15" s="122" t="s">
+      <c r="B15" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="122" t="s">
+      <c r="C15" s="120" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="122"/>
-      <c r="E15" s="144">
+      <c r="D15" s="120"/>
+      <c r="E15" s="142">
         <v>3.43</v>
       </c>
-      <c r="F15" s="124">
-        <v>135708.07</v>
-      </c>
-      <c r="G15" s="133"/>
-      <c r="H15" s="125">
+      <c r="F15" s="122">
+        <v>326059.07</v>
+      </c>
+      <c r="G15" s="131">
+        <v>279558</v>
+      </c>
+      <c r="H15" s="123">
         <f t="shared" si="0"/>
-        <v>135708.07</v>
-      </c>
-      <c r="I15" s="125">
+        <v>46501.070000000007</v>
+      </c>
+      <c r="I15" s="123">
         <f t="shared" si="3"/>
-        <v>4071.2420999999999</v>
-      </c>
-      <c r="J15" s="126">
+        <v>1395.0321000000001</v>
+      </c>
+      <c r="J15" s="124">
         <f t="shared" si="4"/>
         <v>186279.72628300005</v>
       </c>
-      <c r="K15" s="127">
+      <c r="K15" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L15" s="128">
+      <c r="L15" s="126">
         <f t="shared" si="1"/>
-        <v>326059.07</v>
-      </c>
-      <c r="M15" s="129">
+        <v>234176.07</v>
+      </c>
+      <c r="M15" s="127">
         <f t="shared" si="2"/>
-        <v>335841.07</v>
+        <v>241201.07</v>
       </c>
       <c r="N15" s="42">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O15" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="122">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="120">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="B16" s="122" t="s">
+      <c r="B16" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="122" t="s">
+      <c r="C16" s="120" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="130" t="s">
-        <v>144</v>
-      </c>
-      <c r="E16" s="144">
+      <c r="D16" s="128" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" s="142">
         <v>2.95</v>
       </c>
-      <c r="F16" s="124">
-        <v>116717.08</v>
-      </c>
-      <c r="G16" s="133"/>
-      <c r="H16" s="125">
+      <c r="F16" s="122">
+        <v>280430.08000000002</v>
+      </c>
+      <c r="G16" s="131"/>
+      <c r="H16" s="123">
         <f t="shared" si="0"/>
-        <v>116717.08</v>
-      </c>
-      <c r="I16" s="125">
+        <v>280430.08000000002</v>
+      </c>
+      <c r="I16" s="123">
         <f t="shared" si="3"/>
-        <v>3501.5124000000001</v>
-      </c>
-      <c r="J16" s="126">
+        <v>8412.9024000000009</v>
+      </c>
+      <c r="J16" s="124">
         <f t="shared" si="4"/>
         <v>160211.42639500002</v>
       </c>
-      <c r="K16" s="127">
+      <c r="K16" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L16" s="128">
+      <c r="L16" s="126">
         <f t="shared" si="1"/>
-        <v>280430.08000000002</v>
-      </c>
-      <c r="M16" s="129">
+        <v>449054.08</v>
+      </c>
+      <c r="M16" s="127">
         <f t="shared" si="2"/>
-        <v>288843.08</v>
+        <v>462526.08</v>
       </c>
       <c r="N16" s="42">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="122">
+    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="120">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="B17" s="122" t="s">
+      <c r="B17" s="120" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="122" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="130" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="144">
+      <c r="C17" s="120" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="128" t="s">
+        <v>166</v>
+      </c>
+      <c r="E17" s="142">
         <v>5.69</v>
       </c>
-      <c r="F17" s="124">
-        <v>225125.09</v>
-      </c>
-      <c r="G17" s="133"/>
-      <c r="H17" s="125">
+      <c r="F17" s="122">
+        <v>540897.09</v>
+      </c>
+      <c r="G17" s="131">
+        <f>F17</f>
+        <v>540897.09</v>
+      </c>
+      <c r="H17" s="123">
         <f t="shared" si="0"/>
-        <v>225125.09</v>
-      </c>
-      <c r="I17" s="125">
+        <v>0</v>
+      </c>
+      <c r="I17" s="123">
         <f t="shared" si="3"/>
-        <v>6753.7527</v>
-      </c>
-      <c r="J17" s="126">
+        <v>0</v>
+      </c>
+      <c r="J17" s="124">
         <f t="shared" si="4"/>
         <v>309017.97158900008</v>
       </c>
-      <c r="K17" s="127">
+      <c r="K17" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L17" s="128">
+      <c r="L17" s="126">
         <f t="shared" si="1"/>
-        <v>540897.09</v>
-      </c>
-      <c r="M17" s="129">
+        <v>309018.09000000003</v>
+      </c>
+      <c r="M17" s="127">
         <f t="shared" si="2"/>
-        <v>557124.09</v>
+        <v>318289.09000000003</v>
       </c>
       <c r="N17" s="42">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="122">
+    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="120">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="B18" s="122" t="s">
+      <c r="B18" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="122" t="s">
+      <c r="C18" s="120" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="130" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" s="144">
+      <c r="D18" s="128" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="142">
         <v>3.43</v>
       </c>
-      <c r="F18" s="124">
-        <v>419164.1</v>
-      </c>
-      <c r="G18" s="133">
-        <f>F18</f>
-        <v>419164.1</v>
-      </c>
-      <c r="H18" s="125">
+      <c r="F18" s="122">
+        <v>186280.1</v>
+      </c>
+      <c r="G18" s="131">
+        <v>191868.1</v>
+      </c>
+      <c r="H18" s="123">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="125">
+        <v>-5588</v>
+      </c>
+      <c r="I18" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J18" s="126">
+      <c r="J18" s="124">
         <f t="shared" si="4"/>
         <v>186279.72628300005</v>
       </c>
-      <c r="K18" s="127">
+      <c r="K18" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L18" s="128">
+      <c r="L18" s="126">
         <f t="shared" si="1"/>
-        <v>186280.1</v>
-      </c>
-      <c r="M18" s="129">
+        <v>180692.1</v>
+      </c>
+      <c r="M18" s="127">
         <f t="shared" si="2"/>
-        <v>191868.1</v>
+        <v>186113.1</v>
       </c>
       <c r="N18" s="42">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="122">
+    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="120">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="B19" s="122" t="s">
+      <c r="B19" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="122" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="130" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" s="144">
+      <c r="C19" s="120" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="128" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="142">
         <v>2.95</v>
       </c>
-      <c r="F19" s="124">
-        <v>113321.11</v>
-      </c>
-      <c r="G19" s="133">
+      <c r="F19" s="122">
+        <v>160211.10999999999</v>
+      </c>
+      <c r="G19" s="131">
         <f>F19</f>
-        <v>113321.11</v>
-      </c>
-      <c r="H19" s="125">
+        <v>160211.10999999999</v>
+      </c>
+      <c r="H19" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="125">
+      <c r="I19" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J19" s="126">
+      <c r="J19" s="124">
         <f t="shared" si="4"/>
         <v>160211.42639500002</v>
       </c>
-      <c r="K19" s="127">
+      <c r="K19" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L19" s="128">
+      <c r="L19" s="126">
         <f t="shared" si="1"/>
         <v>160211.10999999999</v>
       </c>
-      <c r="M19" s="129">
+      <c r="M19" s="127">
         <f t="shared" si="2"/>
         <v>165017.10999999999</v>
       </c>
@@ -3994,158 +3890,157 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="122">
+    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="120">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="B20" s="122" t="s">
+      <c r="B20" s="120" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="122" t="s">
-        <v>122</v>
-      </c>
-      <c r="D20" s="130" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" s="144">
+      <c r="C20" s="120" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="128" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="142">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F20" s="124">
-        <v>245082.12</v>
-      </c>
-      <c r="G20" s="133">
-        <f>F20</f>
-        <v>245082.12</v>
-      </c>
-      <c r="H20" s="125">
+      <c r="F20" s="122">
+        <v>336716.12</v>
+      </c>
+      <c r="G20" s="131">
+        <v>346814.12</v>
+      </c>
+      <c r="H20" s="123">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="125">
+        <v>-10098</v>
+      </c>
+      <c r="I20" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J20" s="126">
+      <c r="J20" s="124">
         <f t="shared" si="4"/>
         <v>336715.54022000002</v>
       </c>
-      <c r="K20" s="127">
+      <c r="K20" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L20" s="128">
+      <c r="L20" s="126">
         <f t="shared" si="1"/>
-        <v>336716.12</v>
-      </c>
-      <c r="M20" s="129">
+        <v>326618.12</v>
+      </c>
+      <c r="M20" s="127">
         <f t="shared" si="2"/>
-        <v>346817.12</v>
+        <v>336417.12</v>
       </c>
       <c r="N20" s="42">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="122">
+    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="120">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="B21" s="122" t="s">
+      <c r="B21" s="120" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="122" t="s">
+      <c r="C21" s="120" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="130" t="s">
-        <v>131</v>
-      </c>
-      <c r="E21" s="144">
+      <c r="D21" s="128" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="142">
         <v>3.43</v>
       </c>
-      <c r="F21" s="124">
-        <v>135708.13</v>
-      </c>
-      <c r="G21" s="133">
-        <f>F21+5406.25</f>
-        <v>141114.38</v>
-      </c>
-      <c r="H21" s="125">
+      <c r="F21" s="122">
+        <v>180873.13</v>
+      </c>
+      <c r="G21" s="131">
+        <f>F21</f>
+        <v>180873.13</v>
+      </c>
+      <c r="H21" s="123">
         <f t="shared" si="0"/>
-        <v>-5406.25</v>
-      </c>
-      <c r="I21" s="125">
+        <v>0</v>
+      </c>
+      <c r="I21" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="126">
+      <c r="J21" s="124">
         <f t="shared" si="4"/>
         <v>186279.72628300005</v>
       </c>
-      <c r="K21" s="127">
+      <c r="K21" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L21" s="128">
+      <c r="L21" s="126">
         <f t="shared" si="1"/>
-        <v>180873.13</v>
-      </c>
-      <c r="M21" s="129">
+        <v>186280.13</v>
+      </c>
+      <c r="M21" s="127">
         <f t="shared" si="2"/>
-        <v>186299.13</v>
+        <v>191868.13</v>
       </c>
       <c r="N21" s="42">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="122">
+    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="120">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="120" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="122" t="s">
+      <c r="C22" s="120" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="130" t="s">
-        <v>139</v>
-      </c>
-      <c r="E22" s="144">
+      <c r="D22" s="128" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" s="142">
         <v>2.95</v>
       </c>
-      <c r="F22" s="124">
-        <v>116717.14</v>
-      </c>
-      <c r="G22" s="133">
+      <c r="F22" s="122">
+        <v>160211.14000000001</v>
+      </c>
+      <c r="G22" s="131">
         <f>F22</f>
-        <v>116717.14</v>
-      </c>
-      <c r="H22" s="125">
+        <v>160211.14000000001</v>
+      </c>
+      <c r="H22" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="125">
+      <c r="I22" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J22" s="126">
+      <c r="J22" s="124">
         <f t="shared" si="4"/>
         <v>160211.42639500002</v>
       </c>
-      <c r="K22" s="127">
+      <c r="K22" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L22" s="128">
+      <c r="L22" s="126">
         <f t="shared" si="1"/>
         <v>160211.14000000001</v>
       </c>
-      <c r="M22" s="129">
+      <c r="M22" s="127">
         <f t="shared" si="2"/>
         <v>165017.14000000001</v>
       </c>
@@ -4154,52 +4049,52 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="131">
+    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="129">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="B23" s="131" t="s">
+      <c r="B23" s="129" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="131" t="s">
+      <c r="C23" s="129" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="132" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" s="145">
+      <c r="D23" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" s="143">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F23" s="133">
-        <v>245303.15</v>
+      <c r="F23" s="131">
+        <v>336716.15</v>
       </c>
       <c r="G23" s="133">
         <f>F23</f>
-        <v>245303.15</v>
-      </c>
-      <c r="H23" s="125">
+        <v>336716.15</v>
+      </c>
+      <c r="H23" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23" s="125">
+      <c r="I23" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J23" s="126">
+      <c r="J23" s="124">
         <f t="shared" si="4"/>
         <v>336715.54022000002</v>
       </c>
-      <c r="K23" s="127">
+      <c r="K23" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L23" s="128">
+      <c r="L23" s="126">
         <f t="shared" si="1"/>
         <v>336716.15</v>
       </c>
-      <c r="M23" s="129">
+      <c r="M23" s="127">
         <f t="shared" si="2"/>
         <v>346817.15</v>
       </c>
@@ -4208,102 +4103,101 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="131">
+    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="129">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="B24" s="131" t="s">
+      <c r="B24" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="131" t="s">
+      <c r="C24" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="131"/>
-      <c r="E24" s="144">
+      <c r="D24" s="129"/>
+      <c r="E24" s="142">
         <v>3.43</v>
       </c>
-      <c r="F24" s="124">
-        <v>271294.15999999997</v>
-      </c>
-      <c r="G24" s="133">
-        <f>267345.16+3949</f>
-        <v>271294.15999999997</v>
-      </c>
-      <c r="H24" s="125">
+      <c r="F24" s="122">
+        <v>186280.16</v>
+      </c>
+      <c r="G24" s="131">
+        <v>191868.16</v>
+      </c>
+      <c r="H24" s="123">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="125">
+        <v>-5588</v>
+      </c>
+      <c r="I24" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="126">
+      <c r="J24" s="124">
         <f t="shared" si="4"/>
         <v>186279.72628300005</v>
       </c>
-      <c r="K24" s="127">
+      <c r="K24" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L24" s="128">
+      <c r="L24" s="126">
         <f t="shared" si="1"/>
-        <v>186280.16</v>
-      </c>
-      <c r="M24" s="129">
+        <v>180692.16</v>
+      </c>
+      <c r="M24" s="127">
         <f t="shared" si="2"/>
-        <v>191868.16</v>
+        <v>186113.16</v>
       </c>
       <c r="N24" s="42">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="122">
+    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="120">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="B25" s="122" t="s">
+      <c r="B25" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="122" t="s">
+      <c r="C25" s="120" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="130" t="s">
-        <v>140</v>
-      </c>
-      <c r="E25" s="144">
+      <c r="D25" s="128" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" s="142">
         <v>2.95</v>
       </c>
-      <c r="F25" s="133">
-        <v>116717.17</v>
+      <c r="F25" s="131">
+        <v>160211.17000000001</v>
       </c>
       <c r="G25" s="133">
         <f>F25</f>
-        <v>116717.17</v>
-      </c>
-      <c r="H25" s="125">
+        <v>160211.17000000001</v>
+      </c>
+      <c r="H25" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I25" s="125">
+      <c r="I25" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="126">
+      <c r="J25" s="124">
         <f t="shared" si="4"/>
         <v>160211.42639500002</v>
       </c>
-      <c r="K25" s="127">
+      <c r="K25" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L25" s="128">
+      <c r="L25" s="126">
         <f t="shared" si="1"/>
         <v>160211.17000000001</v>
       </c>
-      <c r="M25" s="129">
+      <c r="M25" s="127">
         <f t="shared" si="2"/>
         <v>165017.17000000001</v>
       </c>
@@ -4312,152 +4206,153 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="131">
+    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="129">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="B26" s="131" t="s">
+      <c r="B26" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="131" t="s">
+      <c r="C26" s="129" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="154"/>
-      <c r="E26" s="145">
+      <c r="D26" s="152"/>
+      <c r="E26" s="143">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F26" s="133">
-        <v>252662.18</v>
+      <c r="F26" s="131">
+        <v>344295.18</v>
       </c>
       <c r="G26" s="133">
-        <v>245303.18</v>
-      </c>
-      <c r="H26" s="125">
+        <f>F26</f>
+        <v>344295.18</v>
+      </c>
+      <c r="H26" s="123">
         <f t="shared" si="0"/>
-        <v>7359</v>
-      </c>
-      <c r="I26" s="125">
+        <v>0</v>
+      </c>
+      <c r="I26" s="123">
         <f t="shared" si="3"/>
-        <v>220.76999999999998</v>
-      </c>
-      <c r="J26" s="126">
+        <v>0</v>
+      </c>
+      <c r="J26" s="124">
         <f t="shared" si="4"/>
         <v>336715.54022000002</v>
       </c>
-      <c r="K26" s="127">
+      <c r="K26" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L26" s="128">
+      <c r="L26" s="126">
         <f t="shared" si="1"/>
-        <v>344295.18</v>
-      </c>
-      <c r="M26" s="129">
+        <v>336716.18</v>
+      </c>
+      <c r="M26" s="127">
         <f t="shared" si="2"/>
-        <v>354624.18</v>
+        <v>346817.18</v>
       </c>
       <c r="N26" s="42">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="131">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="129">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="B27" s="131" t="s">
+      <c r="B27" s="129" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="131" t="s">
-        <v>125</v>
-      </c>
-      <c r="D27" s="132" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" s="145">
+      <c r="C27" s="129" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="130" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="143">
         <v>3.43</v>
       </c>
-      <c r="F27" s="133">
-        <v>460172.19</v>
-      </c>
-      <c r="G27" s="133"/>
-      <c r="H27" s="125">
+      <c r="F27" s="131">
+        <v>660257.18999999994</v>
+      </c>
+      <c r="G27" s="131"/>
+      <c r="H27" s="123">
         <f t="shared" si="0"/>
-        <v>460172.19</v>
-      </c>
-      <c r="I27" s="125">
+        <v>660257.18999999994</v>
+      </c>
+      <c r="I27" s="123">
         <f t="shared" si="3"/>
-        <v>13805.1657</v>
-      </c>
-      <c r="J27" s="126">
+        <v>19807.715699999997</v>
+      </c>
+      <c r="J27" s="124">
         <f t="shared" si="4"/>
         <v>186279.72628300005</v>
       </c>
-      <c r="K27" s="127">
+      <c r="K27" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L27" s="128">
+      <c r="L27" s="126">
         <f t="shared" si="1"/>
-        <v>660257.18999999994</v>
-      </c>
-      <c r="M27" s="129">
+        <v>866345.19</v>
+      </c>
+      <c r="M27" s="127">
         <f t="shared" si="2"/>
-        <v>680065.19</v>
+        <v>892335.19</v>
       </c>
       <c r="N27" s="42">
         <f t="shared" si="7"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="131">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="129">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="B28" s="155" t="s">
+      <c r="B28" s="153" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="131" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" s="132" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" s="145">
+      <c r="C28" s="129" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" s="143">
         <v>2.95</v>
       </c>
-      <c r="F28" s="135">
-        <v>116717.2</v>
-      </c>
-      <c r="G28" s="133">
+      <c r="F28" s="133">
+        <v>160211.20000000001</v>
+      </c>
+      <c r="G28" s="131">
         <f>F28</f>
-        <v>116717.2</v>
-      </c>
-      <c r="H28" s="125">
+        <v>160211.20000000001</v>
+      </c>
+      <c r="H28" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I28" s="125">
+      <c r="I28" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J28" s="126">
+      <c r="J28" s="124">
         <f t="shared" si="4"/>
         <v>160211.42639500002</v>
       </c>
-      <c r="K28" s="127">
+      <c r="K28" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L28" s="128">
+      <c r="L28" s="126">
         <f t="shared" si="1"/>
         <v>160211.20000000001</v>
       </c>
-      <c r="M28" s="129">
+      <c r="M28" s="127">
         <f t="shared" si="2"/>
         <v>165017.20000000001</v>
       </c>
@@ -4466,154 +4361,154 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="131">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="129">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="B29" s="155" t="s">
+      <c r="B29" s="153" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="156" t="s">
+      <c r="C29" s="154" t="s">
         <v>100</v>
       </c>
-      <c r="D29" s="132"/>
-      <c r="E29" s="145">
+      <c r="D29" s="130"/>
+      <c r="E29" s="143">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F29" s="135">
-        <v>238441.21</v>
-      </c>
-      <c r="G29" s="133">
-        <v>245594.21</v>
-      </c>
-      <c r="H29" s="125">
+      <c r="F29" s="133">
+        <v>329563.21000000002</v>
+      </c>
+      <c r="G29" s="131">
+        <v>339450.21</v>
+      </c>
+      <c r="H29" s="123">
         <f t="shared" si="0"/>
-        <v>-7153</v>
-      </c>
-      <c r="I29" s="125">
+        <v>-9887</v>
+      </c>
+      <c r="I29" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="126">
+      <c r="J29" s="124">
         <f t="shared" si="4"/>
         <v>336715.54022000002</v>
       </c>
-      <c r="K29" s="127">
+      <c r="K29" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L29" s="128">
+      <c r="L29" s="126">
         <f t="shared" si="1"/>
-        <v>329563.21000000002</v>
-      </c>
-      <c r="M29" s="129">
+        <v>326829.21000000002</v>
+      </c>
+      <c r="M29" s="127">
         <f t="shared" si="2"/>
-        <v>339450.21</v>
+        <v>336634.21</v>
       </c>
       <c r="N29" s="42">
         <f t="shared" si="7"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="131">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="129">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="B30" s="157" t="s">
+      <c r="B30" s="155" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="131" t="s">
+      <c r="C30" s="129" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="132" t="s">
-        <v>153</v>
-      </c>
-      <c r="E30" s="145">
+      <c r="D30" s="130" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" s="143">
         <v>3.43</v>
       </c>
-      <c r="F30" s="135">
-        <v>130534.22</v>
-      </c>
-      <c r="G30" s="135">
-        <v>0</v>
-      </c>
-      <c r="H30" s="125">
+      <c r="F30" s="133">
+        <v>320730.21999999997</v>
+      </c>
+      <c r="G30" s="133">
+        <v>140000</v>
+      </c>
+      <c r="H30" s="123">
         <f t="shared" si="0"/>
-        <v>130534.22</v>
-      </c>
-      <c r="I30" s="125">
+        <v>180730.21999999997</v>
+      </c>
+      <c r="I30" s="123">
         <f t="shared" si="3"/>
-        <v>3916.0265999999997</v>
-      </c>
-      <c r="J30" s="126">
+        <v>5421.9065999999993</v>
+      </c>
+      <c r="J30" s="124">
         <f t="shared" si="4"/>
         <v>186279.72628300005</v>
       </c>
-      <c r="K30" s="127">
+      <c r="K30" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L30" s="128">
+      <c r="L30" s="126">
         <f t="shared" si="1"/>
-        <v>320730.21999999997</v>
-      </c>
-      <c r="M30" s="129">
+        <v>372432.22</v>
+      </c>
+      <c r="M30" s="127">
         <f t="shared" si="2"/>
-        <v>330352.21999999997</v>
+        <v>383605.22</v>
       </c>
       <c r="N30" s="42">
         <f t="shared" si="7"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="131">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="129">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="B31" s="157" t="s">
+      <c r="B31" s="155" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="158" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" s="159" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31" s="145">
+      <c r="C31" s="156" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="157" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" s="143">
         <v>2.95</v>
       </c>
-      <c r="F31" s="135">
-        <v>116717.23</v>
+      <c r="F31" s="133">
+        <v>160211.23000000001</v>
       </c>
       <c r="G31" s="133">
         <f>F31</f>
-        <v>116717.23</v>
-      </c>
-      <c r="H31" s="125">
+        <v>160211.23000000001</v>
+      </c>
+      <c r="H31" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="125">
+      <c r="I31" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="126">
+      <c r="J31" s="124">
         <f t="shared" si="4"/>
         <v>160211.42639500002</v>
       </c>
-      <c r="K31" s="127">
+      <c r="K31" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L31" s="128">
+      <c r="L31" s="126">
         <f t="shared" si="1"/>
         <v>160211.23000000001</v>
       </c>
-      <c r="M31" s="129">
+      <c r="M31" s="127">
         <f t="shared" si="2"/>
         <v>165017.23000000001</v>
       </c>
@@ -4622,238 +4517,231 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="122">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="120">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="B32" s="136" t="s">
+      <c r="B32" s="134" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="137" t="s">
+      <c r="C32" s="135" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="138"/>
-      <c r="E32" s="144">
+      <c r="D32" s="136"/>
+      <c r="E32" s="142">
         <v>5.68</v>
       </c>
-      <c r="F32" s="134">
-        <v>217987.24</v>
-      </c>
-      <c r="G32" s="135">
-        <v>224527.24</v>
-      </c>
-      <c r="H32" s="125">
+      <c r="F32" s="132">
+        <v>301935.24</v>
+      </c>
+      <c r="G32" s="133">
+        <f>F32</f>
+        <v>301935.24</v>
+      </c>
+      <c r="H32" s="123">
         <f t="shared" si="0"/>
-        <v>-6540</v>
-      </c>
-      <c r="I32" s="125">
+        <v>0</v>
+      </c>
+      <c r="I32" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J32" s="126">
+      <c r="J32" s="124">
         <f t="shared" si="4"/>
         <v>308474.88200799999</v>
       </c>
-      <c r="K32" s="127">
+      <c r="K32" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L32" s="128">
+      <c r="L32" s="126">
         <f t="shared" si="1"/>
-        <v>301935.24</v>
-      </c>
-      <c r="M32" s="129">
+        <v>308475.24</v>
+      </c>
+      <c r="M32" s="127">
         <f t="shared" si="2"/>
-        <v>310993.24</v>
+        <v>317729.24</v>
       </c>
       <c r="N32" s="42">
         <f t="shared" si="7"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="219" t="s">
+    <row r="33" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="199" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="220"/>
-      <c r="C33" s="137" t="s">
+      <c r="B33" s="200"/>
+      <c r="C33" s="135" t="s">
         <v>103</v>
       </c>
-      <c r="D33" s="137"/>
-      <c r="E33" s="123"/>
-      <c r="F33" s="134">
-        <v>53321.25</v>
-      </c>
-      <c r="G33" s="135">
-        <v>54921.25</v>
-      </c>
-      <c r="H33" s="125">
+      <c r="D33" s="135"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="132">
+        <v>158611.25</v>
+      </c>
+      <c r="G33" s="133">
+        <v>163369.25</v>
+      </c>
+      <c r="H33" s="123">
         <f t="shared" si="0"/>
-        <v>-1600</v>
-      </c>
-      <c r="I33" s="125">
+        <v>-4758</v>
+      </c>
+      <c r="I33" s="123">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J33" s="126">
+      <c r="J33" s="124">
         <f>J16</f>
         <v>160211.42639500002</v>
       </c>
-      <c r="K33" s="127">
+      <c r="K33" s="125">
         <f>K16</f>
         <v>0</v>
       </c>
-      <c r="L33" s="128">
+      <c r="L33" s="126">
         <f t="shared" si="1"/>
-        <v>158611.25</v>
-      </c>
-      <c r="M33" s="129">
+        <v>155453.25</v>
+      </c>
+      <c r="M33" s="127">
         <f t="shared" si="2"/>
-        <v>163369.25</v>
+        <v>160117.25</v>
       </c>
       <c r="N33" s="42">
         <f t="shared" si="7"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="O33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="221" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="201" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="221"/>
-      <c r="C34" s="222"/>
-      <c r="D34" s="139"/>
-      <c r="E34" s="147">
+      <c r="B34" s="201"/>
+      <c r="C34" s="202"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="145">
         <f>SUM(E9:E33)</f>
         <v>99.700000000000045</v>
       </c>
-      <c r="F34" s="140">
+      <c r="F34" s="138">
         <f t="shared" ref="F34:K34" si="8">SUM(F9:F33)</f>
-        <v>4714407.2500000009</v>
-      </c>
-      <c r="G34" s="141">
+        <v>6647222.2500000009</v>
+      </c>
+      <c r="G34" s="139">
         <f>SUM(G9:G33)</f>
-        <v>3674269.8400000008</v>
-      </c>
-      <c r="H34" s="141">
+        <v>5515222.6900000013</v>
+      </c>
+      <c r="H34" s="139">
         <f t="shared" si="8"/>
-        <v>1040137.4099999999</v>
-      </c>
-      <c r="I34" s="141">
+        <v>1131999.56</v>
+      </c>
+      <c r="I34" s="139">
         <f t="shared" si="8"/>
-        <v>32268.469500000003</v>
-      </c>
-      <c r="J34" s="142">
+        <v>35037.556799999998</v>
+      </c>
+      <c r="J34" s="140">
         <f t="shared" si="8"/>
         <v>5574814.5489649996</v>
       </c>
-      <c r="K34" s="141">
+      <c r="K34" s="139">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L34" s="143">
+      <c r="L34" s="141">
         <f>SUM(L9:L26)</f>
-        <v>4555702.71</v>
-      </c>
-      <c r="M34" s="143">
+        <v>4391897.71</v>
+      </c>
+      <c r="M34" s="141">
         <f>SUM(M9:M33)</f>
-        <v>6846635.2500000009</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6944108.2500000009</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="49"/>
       <c r="D35" s="49"/>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="189" t="str">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="192" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D37" s="189"/>
-      <c r="E37" s="189"/>
-      <c r="F37" s="189"/>
-      <c r="G37" s="189"/>
-      <c r="H37" s="189"/>
-      <c r="I37" s="189"/>
-      <c r="J37" s="189"/>
-      <c r="K37" s="189"/>
-      <c r="L37" s="189"/>
-    </row>
-    <row r="38" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="189"/>
-      <c r="D38" s="189"/>
-      <c r="E38" s="189"/>
-      <c r="F38" s="189"/>
-      <c r="G38" s="189"/>
-      <c r="H38" s="189"/>
-      <c r="I38" s="189"/>
-      <c r="J38" s="189"/>
-      <c r="K38" s="189"/>
-      <c r="L38" s="189"/>
-    </row>
-    <row r="39" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="189"/>
-      <c r="D39" s="189"/>
-      <c r="E39" s="189"/>
-      <c r="F39" s="189"/>
-      <c r="G39" s="189"/>
-      <c r="H39" s="189"/>
-      <c r="I39" s="189"/>
-      <c r="J39" s="189"/>
-      <c r="K39" s="189"/>
-      <c r="L39" s="189"/>
-    </row>
-    <row r="40" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="189"/>
-      <c r="D40" s="189"/>
-      <c r="E40" s="189"/>
-      <c r="F40" s="189"/>
-      <c r="G40" s="189"/>
-      <c r="H40" s="189"/>
-      <c r="I40" s="189"/>
-      <c r="J40" s="189"/>
-      <c r="K40" s="189"/>
-      <c r="L40" s="189"/>
-    </row>
-    <row r="41" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="189"/>
-      <c r="D41" s="189"/>
-      <c r="E41" s="189"/>
-      <c r="F41" s="189"/>
-      <c r="G41" s="189"/>
-      <c r="H41" s="189"/>
-      <c r="I41" s="189"/>
-      <c r="J41" s="189"/>
-      <c r="K41" s="189"/>
-      <c r="L41" s="189"/>
-    </row>
-    <row r="42" spans="1:15" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="189"/>
-      <c r="D42" s="189"/>
-      <c r="E42" s="189"/>
-      <c r="F42" s="189"/>
-      <c r="G42" s="189"/>
-      <c r="H42" s="189"/>
-      <c r="I42" s="189"/>
-      <c r="J42" s="189"/>
-      <c r="K42" s="189"/>
-      <c r="L42" s="189"/>
+      <c r="D37" s="192"/>
+      <c r="E37" s="192"/>
+      <c r="F37" s="192"/>
+      <c r="G37" s="192"/>
+      <c r="H37" s="192"/>
+      <c r="I37" s="192"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="192"/>
+      <c r="L37" s="192"/>
+    </row>
+    <row r="38" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="192"/>
+      <c r="D38" s="192"/>
+      <c r="E38" s="192"/>
+      <c r="F38" s="192"/>
+      <c r="G38" s="192"/>
+      <c r="H38" s="192"/>
+      <c r="I38" s="192"/>
+      <c r="J38" s="192"/>
+      <c r="K38" s="192"/>
+      <c r="L38" s="192"/>
+    </row>
+    <row r="39" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="192"/>
+      <c r="D39" s="192"/>
+      <c r="E39" s="192"/>
+      <c r="F39" s="192"/>
+      <c r="G39" s="192"/>
+      <c r="H39" s="192"/>
+      <c r="I39" s="192"/>
+      <c r="J39" s="192"/>
+      <c r="K39" s="192"/>
+      <c r="L39" s="192"/>
+    </row>
+    <row r="40" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="192"/>
+      <c r="D40" s="192"/>
+      <c r="E40" s="192"/>
+      <c r="F40" s="192"/>
+      <c r="G40" s="192"/>
+      <c r="H40" s="192"/>
+      <c r="I40" s="192"/>
+      <c r="J40" s="192"/>
+      <c r="K40" s="192"/>
+      <c r="L40" s="192"/>
+    </row>
+    <row r="41" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="192"/>
+      <c r="D41" s="192"/>
+      <c r="E41" s="192"/>
+      <c r="F41" s="192"/>
+      <c r="G41" s="192"/>
+      <c r="H41" s="192"/>
+      <c r="I41" s="192"/>
+      <c r="J41" s="192"/>
+      <c r="K41" s="192"/>
+      <c r="L41" s="192"/>
+    </row>
+    <row r="42" spans="1:15" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="192"/>
+      <c r="D42" s="192"/>
+      <c r="E42" s="192"/>
+      <c r="F42" s="192"/>
+      <c r="G42" s="192"/>
+      <c r="H42" s="192"/>
+      <c r="I42" s="192"/>
+      <c r="J42" s="192"/>
+      <c r="K42" s="192"/>
+      <c r="L42" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C37:L42"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:C34"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="E1:L1"/>
     <mergeCell ref="I7:I8"/>
@@ -4863,6 +4751,14 @@
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="A4:M6"/>
+    <mergeCell ref="C37:L42"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4872,61 +4768,61 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B2:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="182" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="176"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="184" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="185"/>
-      <c r="G4" s="177"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="178"/>
-      <c r="G5" s="177"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="223"/>
-      <c r="C6" s="224"/>
-      <c r="D6" s="224"/>
-      <c r="E6" s="224"/>
-      <c r="F6" s="224"/>
-      <c r="G6" s="225"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="223"/>
-      <c r="C7" s="224"/>
-      <c r="D7" s="224"/>
-      <c r="E7" s="224"/>
-      <c r="F7" s="224"/>
-      <c r="G7" s="225"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="223"/>
-      <c r="C8" s="224"/>
-      <c r="D8" s="224"/>
-      <c r="E8" s="224"/>
-      <c r="F8" s="224"/>
-      <c r="G8" s="225"/>
-    </row>
-    <row r="9" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="226"/>
-      <c r="C9" s="227"/>
-      <c r="D9" s="227"/>
-      <c r="E9" s="227"/>
-      <c r="F9" s="227"/>
-      <c r="G9" s="228"/>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="179" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="180"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="173"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="181" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="182"/>
+      <c r="G4" s="174"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="175"/>
+      <c r="G5" s="174"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="219"/>
+      <c r="C6" s="220"/>
+      <c r="D6" s="220"/>
+      <c r="E6" s="220"/>
+      <c r="F6" s="220"/>
+      <c r="G6" s="221"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="219"/>
+      <c r="C7" s="220"/>
+      <c r="D7" s="220"/>
+      <c r="E7" s="220"/>
+      <c r="F7" s="220"/>
+      <c r="G7" s="221"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="219"/>
+      <c r="C8" s="220"/>
+      <c r="D8" s="220"/>
+      <c r="E8" s="220"/>
+      <c r="F8" s="220"/>
+      <c r="G8" s="221"/>
+    </row>
+    <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="222"/>
+      <c r="C9" s="223"/>
+      <c r="D9" s="223"/>
+      <c r="E9" s="223"/>
+      <c r="F9" s="223"/>
+      <c r="G9" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/2026/ANATOLE FRANCE/Junio/ANATOLE-Junio.xlsx
+++ b/2026/ANATOLE FRANCE/Junio/ANATOLE-Junio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CA83E1-883C-4A72-87DA-60C3BBD807FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504D890E-EC83-4F55-82BF-F6348688CCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$125</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="166">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -342,12 +337,6 @@
     <t>Muñoz Alicia</t>
   </si>
   <si>
-    <t xml:space="preserve">Horacio De la Torre </t>
-  </si>
-  <si>
-    <t>Porteria</t>
-  </si>
-  <si>
     <t>TOTALES</t>
   </si>
   <si>
@@ -432,9 +421,6 @@
     <t>Camila</t>
   </si>
   <si>
-    <t>La porteria paga lo mismo que el 3B</t>
-  </si>
-  <si>
     <t>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</t>
   </si>
   <si>
@@ -535,6 +521,9 @@
   </si>
   <si>
     <t>El total del dinero en cuenta corresponde a CAJA EXTRAORDINARIA</t>
+  </si>
+  <si>
+    <t>Ingreso pago de expensas porteria</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1230,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1499,132 +1488,6 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1633,6 +1496,135 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1711,9 +1703,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1751,9 +1743,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1786,26 +1778,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1838,26 +1813,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2032,30 +1990,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M129"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
-      <c r="B1" s="186" t="s">
+      <c r="B1" s="197" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
+      <c r="C1" s="197"/>
+      <c r="D1" s="197"/>
       <c r="E1" s="61"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="62" t="s">
         <v>26</v>
@@ -2064,16 +2022,16 @@
       <c r="D2" s="62"/>
       <c r="E2" s="63"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
-      <c r="B3" s="187" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="187"/>
-      <c r="D3" s="187"/>
-      <c r="E3" s="188"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="198" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="199"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -2084,12 +2042,12 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="62" t="s">
@@ -2097,7 +2055,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>56</v>
       </c>
@@ -2108,57 +2066,57 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="183" t="s">
-        <v>156</v>
-      </c>
-      <c r="C8" s="183"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="183"/>
-      <c r="C9" s="183"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="183"/>
-      <c r="C10" s="183"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="189" t="s">
-        <v>134</v>
-      </c>
-      <c r="B13" s="189"/>
-      <c r="C13" s="189"/>
-      <c r="D13" s="189"/>
-      <c r="E13" s="189"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="189"/>
-      <c r="B14" s="189"/>
-      <c r="C14" s="189"/>
-      <c r="D14" s="189"/>
-      <c r="E14" s="189"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="189"/>
-      <c r="B15" s="189"/>
-      <c r="C15" s="189"/>
-      <c r="D15" s="189"/>
-      <c r="E15" s="189"/>
-    </row>
-    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="189"/>
-      <c r="B16" s="189"/>
-      <c r="C16" s="189"/>
-      <c r="D16" s="189"/>
-      <c r="E16" s="189"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="196" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="196"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="196"/>
+      <c r="C9" s="196"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="196"/>
+      <c r="C10" s="196"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="200" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="200"/>
+      <c r="C13" s="200"/>
+      <c r="D13" s="200"/>
+      <c r="E13" s="200"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="200"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="200"/>
+      <c r="D14" s="200"/>
+      <c r="E14" s="200"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="200"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="200"/>
+      <c r="E15" s="200"/>
+    </row>
+    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="200"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="200"/>
+      <c r="E16" s="200"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2167,7 +2125,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>31</v>
       </c>
@@ -2176,20 +2134,20 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
     </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="184" t="s">
-        <v>113</v>
-      </c>
-      <c r="B22" s="185"/>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="191" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" s="192"/>
       <c r="C22" s="5"/>
       <c r="D22" s="159">
         <v>1719538.75</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="70" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B23" s="112"/>
       <c r="C23" s="5"/>
@@ -2198,9 +2156,9 @@
       </c>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="70" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B24" s="112"/>
       <c r="C24" s="5"/>
@@ -2209,7 +2167,7 @@
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="54" t="s">
         <v>32</v>
       </c>
@@ -2222,7 +2180,7 @@
       <c r="E25" s="102"/>
       <c r="G25" s="21"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
@@ -2231,28 +2189,28 @@
       <c r="D26" s="159"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="28"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="159"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="159"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="161"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>36</v>
       </c>
@@ -2261,7 +2219,7 @@
       <c r="D30" s="161"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="54" t="s">
         <v>32</v>
       </c>
@@ -2273,7 +2231,7 @@
       </c>
       <c r="E31" s="102"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="29" t="s">
         <v>1</v>
       </c>
@@ -2286,7 +2244,7 @@
       </c>
       <c r="F32" s="21"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
         <v>18</v>
       </c>
@@ -2295,33 +2253,33 @@
       <c r="D33" s="164"/>
       <c r="E33" s="104"/>
     </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="190" t="s">
-        <v>135</v>
-      </c>
-      <c r="B34" s="191"/>
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="187" t="s">
+        <v>132</v>
+      </c>
+      <c r="B34" s="188"/>
       <c r="C34" s="51"/>
       <c r="D34" s="159">
         <v>45000</v>
       </c>
-      <c r="E34" s="225" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="190" t="s">
+      <c r="E34" s="183" t="s">
         <v>159</v>
       </c>
-      <c r="B35" s="191"/>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="187" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="188"/>
       <c r="C35" s="51"/>
-      <c r="D35" s="227">
+      <c r="D35" s="185">
         <v>190000</v>
       </c>
-      <c r="E35" s="226" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E35" s="184" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
         <v>15</v>
       </c>
@@ -2333,7 +2291,7 @@
         <v>235000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="34" t="s">
         <v>29</v>
       </c>
@@ -2342,20 +2300,20 @@
       <c r="D37" s="166"/>
       <c r="E37" s="105"/>
     </row>
-    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="184" t="s">
-        <v>145</v>
-      </c>
-      <c r="B38" s="185"/>
+    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="191" t="s">
+        <v>142</v>
+      </c>
+      <c r="B38" s="192"/>
       <c r="C38" s="52"/>
       <c r="D38" s="167">
         <v>161303</v>
       </c>
       <c r="E38" s="119" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="29" t="s">
         <v>2</v>
       </c>
@@ -2367,7 +2325,7 @@
         <v>161303</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="34" t="s">
         <v>16</v>
       </c>
@@ -2376,42 +2334,42 @@
       <c r="D40" s="168"/>
       <c r="E40" s="108"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="51"/>
-      <c r="D41" s="228">
+      <c r="D41" s="186">
         <v>641714.36</v>
       </c>
       <c r="E41" s="113" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G41" s="89"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="169">
         <v>47994.65</v>
       </c>
       <c r="E42" s="113" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="str">
         <f>A42</f>
         <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="169">
@@ -2422,13 +2380,13 @@
         <v>Transf 12/05</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="169">
@@ -2439,7 +2397,7 @@
         <v>Transf 12/05</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
         <v>3</v>
       </c>
@@ -2451,7 +2409,7 @@
         <v>786848.36</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="34" t="s">
         <v>17</v>
       </c>
@@ -2460,9 +2418,9 @@
       <c r="D46" s="168"/>
       <c r="E46" s="108"/>
     </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2470,12 +2428,12 @@
         <v>413737.24</v>
       </c>
       <c r="E47" s="113" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="176" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B48" s="177"/>
       <c r="C48" s="5"/>
@@ -2483,12 +2441,12 @@
         <v>17281.75</v>
       </c>
       <c r="E48" s="113" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="70" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B49" s="112"/>
       <c r="C49" s="5"/>
@@ -2496,10 +2454,10 @@
         <v>1033943.24</v>
       </c>
       <c r="E49" s="113" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
         <v>4</v>
       </c>
@@ -2511,16 +2469,16 @@
         <v>1464962.23</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="34" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B51" s="29"/>
       <c r="C51" s="29"/>
       <c r="D51" s="165"/>
       <c r="E51" s="109"/>
     </row>
-    <row r="52" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="116" t="s">
         <v>57</v>
       </c>
@@ -2530,12 +2488,12 @@
         <v>189500</v>
       </c>
       <c r="E52" s="144" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="116" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B53" s="112"/>
       <c r="C53" s="5"/>
@@ -2543,38 +2501,38 @@
         <v>38400</v>
       </c>
       <c r="E53" s="144" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="184" t="s">
-        <v>151</v>
-      </c>
-      <c r="B54" s="185"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="191" t="s">
+        <v>148</v>
+      </c>
+      <c r="B54" s="192"/>
       <c r="C54" s="5"/>
       <c r="D54" s="169">
         <v>847000</v>
       </c>
       <c r="E54" s="144" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="184" t="s">
-        <v>161</v>
-      </c>
-      <c r="B55" s="185"/>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="191" t="s">
+        <v>158</v>
+      </c>
+      <c r="B55" s="192"/>
       <c r="C55" s="5"/>
       <c r="D55" s="169">
         <v>847000</v>
       </c>
       <c r="E55" s="144" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="116" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B56" s="112"/>
       <c r="C56" s="5"/>
@@ -2582,10 +2540,10 @@
         <v>60000</v>
       </c>
       <c r="E56" s="144" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="29" t="s">
         <v>8</v>
       </c>
@@ -2597,7 +2555,7 @@
         <v>1981900</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="34" t="s">
         <v>11</v>
       </c>
@@ -2606,7 +2564,7 @@
       <c r="D58" s="163"/>
       <c r="E58" s="109"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>53</v>
       </c>
@@ -2617,7 +2575,7 @@
       </c>
       <c r="E59" s="111"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>52</v>
       </c>
@@ -2628,7 +2586,7 @@
       </c>
       <c r="E60" s="39"/>
     </row>
-    <row r="61" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="50" t="s">
         <v>15</v>
       </c>
@@ -2640,14 +2598,14 @@
         <v>164455.99</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="67"/>
       <c r="E62" s="75"/>
     </row>
-    <row r="63" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="30" t="s">
         <v>46</v>
       </c>
@@ -2656,13 +2614,13 @@
       <c r="D63" s="76"/>
       <c r="E63" s="77"/>
     </row>
-    <row r="64" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="D64" s="78"/>
       <c r="E64" s="79"/>
       <c r="F64" s="42"/>
     </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>12</v>
       </c>
@@ -2681,7 +2639,7 @@
       <c r="K65" s="89"/>
       <c r="L65" s="89"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D66" s="78"/>
       <c r="E66" s="78"/>
       <c r="H66" s="89"/>
@@ -2690,12 +2648,12 @@
       <c r="K66" s="89"/>
       <c r="L66" s="89"/>
     </row>
-    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D67" s="78"/>
       <c r="E67" s="78"/>
       <c r="H67" s="118"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
         <v>41</v>
       </c>
@@ -2704,35 +2662,35 @@
       <c r="D68" s="82"/>
       <c r="E68" s="83"/>
     </row>
-    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="184"/>
-      <c r="B69" s="185"/>
+    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="191"/>
+      <c r="B69" s="192"/>
       <c r="C69" s="5"/>
       <c r="D69" s="93"/>
       <c r="E69" s="69"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="184"/>
-      <c r="B70" s="185"/>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="191"/>
+      <c r="B70" s="192"/>
       <c r="C70" s="5"/>
       <c r="D70" s="71"/>
       <c r="E70" s="69"/>
     </row>
-    <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="190"/>
-      <c r="B71" s="191"/>
+    <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="187"/>
+      <c r="B71" s="188"/>
       <c r="C71" s="5"/>
       <c r="D71" s="71"/>
       <c r="E71" s="69"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="70"/>
       <c r="B72" s="72"/>
       <c r="C72" s="5"/>
       <c r="D72" s="71"/>
       <c r="E72" s="69"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="48"/>
       <c r="B73" s="47"/>
       <c r="C73" s="47"/>
@@ -2742,9 +2700,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="147" t="s">
         <v>19</v>
       </c>
@@ -2755,8 +2713,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>20</v>
       </c>
@@ -2768,8 +2726,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="65" t="s">
         <v>13</v>
       </c>
@@ -2778,7 +2736,7 @@
         <v>6088422.5800000001</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="65" t="s">
         <v>14</v>
       </c>
@@ -2787,7 +2745,7 @@
         <v>6088422.5800000001</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="65" t="s">
         <v>21</v>
       </c>
@@ -2796,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="65" t="s">
         <v>37</v>
       </c>
@@ -2805,59 +2763,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="192"/>
-      <c r="B86" s="192"/>
-      <c r="C86" s="192"/>
-      <c r="D86" s="192"/>
-      <c r="E86" s="192"/>
-    </row>
-    <row r="87" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="192"/>
-      <c r="B87" s="192"/>
-      <c r="C87" s="192"/>
-      <c r="D87" s="192"/>
-      <c r="E87" s="192"/>
-    </row>
-    <row r="88" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="192"/>
-      <c r="B88" s="192"/>
-      <c r="C88" s="192"/>
-      <c r="D88" s="192"/>
-      <c r="E88" s="192"/>
-    </row>
-    <row r="90" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="189"/>
+      <c r="B86" s="189"/>
+      <c r="C86" s="189"/>
+      <c r="D86" s="189"/>
+      <c r="E86" s="189"/>
+    </row>
+    <row r="87" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="189"/>
+      <c r="B87" s="189"/>
+      <c r="C87" s="189"/>
+      <c r="D87" s="189"/>
+      <c r="E87" s="189"/>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="189"/>
+      <c r="B88" s="189"/>
+      <c r="C88" s="189"/>
+      <c r="D88" s="189"/>
+      <c r="E88" s="189"/>
+    </row>
+    <row r="90" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="22"/>
       <c r="B90" s="90"/>
       <c r="C90" s="23"/>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="32"/>
       <c r="B91" s="56">
         <v>0</v>
       </c>
       <c r="C91" s="25"/>
     </row>
-    <row r="92" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="24" t="s">
         <v>7</v>
       </c>
       <c r="B92" s="39">
         <f>PRORRATEO!G34</f>
-        <v>5515222.6900000013</v>
+        <v>5351853.4400000013</v>
       </c>
       <c r="C92" s="23"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="24"/>
       <c r="B93" s="39">
         <v>0</v>
       </c>
       <c r="C93" s="23"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="24" t="s">
         <v>38</v>
       </c>
@@ -2867,19 +2825,19 @@
       </c>
       <c r="C94" s="23"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="27"/>
       <c r="B95" s="46"/>
       <c r="C95" s="23"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="88" t="s">
         <v>42</v>
       </c>
       <c r="B96" s="46"/>
       <c r="C96" s="23"/>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="38" t="s">
         <v>22</v>
       </c>
@@ -2889,7 +2847,7 @@
       </c>
       <c r="C97" s="23"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="27" t="s">
         <v>23</v>
       </c>
@@ -2899,36 +2857,36 @@
       </c>
       <c r="C98" s="23"/>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B99" s="56">
         <f>SUM(B91:B98)</f>
-        <v>-573199.88999999873</v>
+        <v>-736569.13999999873</v>
       </c>
       <c r="C99" s="26"/>
       <c r="D99" s="42"/>
     </row>
-    <row r="100" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="40"/>
       <c r="C100" s="26"/>
       <c r="D100" s="42"/>
       <c r="E100" s="91"/>
       <c r="F100" s="92"/>
     </row>
-    <row r="101" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="41"/>
       <c r="C101" s="26"/>
     </row>
-    <row r="102" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102"/>
       <c r="B102" s="40"/>
       <c r="C102" s="36"/>
     </row>
-    <row r="103" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="95" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B103" s="146">
         <v>4130734.6900000004</v>
@@ -2937,7 +2895,7 @@
       <c r="D103" s="45"/>
       <c r="E103" s="42"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="52" t="s">
         <v>47</v>
       </c>
@@ -2946,7 +2904,7 @@
         <v>-6088422.5800000001</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="52" t="s">
         <v>48</v>
       </c>
@@ -2955,15 +2913,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="B106" s="158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="B106" s="229">
+        <v>163369.25</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="52" t="s">
         <v>51</v>
       </c>
@@ -2972,16 +2930,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="52" t="s">
         <v>49</v>
       </c>
       <c r="B108" s="100">
         <f>PRORRATEO!G34</f>
-        <v>5515222.6900000013</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5351853.4400000013</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="97" t="s">
         <v>44</v>
       </c>
@@ -2992,58 +2950,58 @@
       <c r="D109" s="42"/>
       <c r="E109" s="42"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="96"/>
       <c r="B110" s="96"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="96"/>
       <c r="B111" s="96"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="194" t="s">
-        <v>167</v>
-      </c>
-      <c r="B112" s="194"/>
-    </row>
-    <row r="113" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="195"/>
-      <c r="B113" s="195"/>
-    </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="195"/>
-      <c r="B114" s="195"/>
-    </row>
-    <row r="115" spans="1:13" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="196"/>
-      <c r="B115" s="196"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="193" t="s">
+        <v>164</v>
+      </c>
+      <c r="B112" s="193"/>
+    </row>
+    <row r="113" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="194"/>
+      <c r="B113" s="194"/>
+    </row>
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="194"/>
+      <c r="B114" s="194"/>
+    </row>
+    <row r="115" spans="1:13" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="195"/>
+      <c r="B115" s="195"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="96"/>
       <c r="B116" s="96"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="96"/>
       <c r="B117" s="96"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="96"/>
       <c r="B118" s="96"/>
     </row>
-    <row r="119" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="193" t="s">
+    <row r="119" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A120" s="190" t="s">
         <v>30</v>
       </c>
-      <c r="B120" s="193"/>
-      <c r="C120" s="193"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="193"/>
-      <c r="B121" s="193"/>
-      <c r="C121" s="193"/>
-    </row>
-    <row r="122" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="190"/>
+      <c r="C120" s="190"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="190"/>
+      <c r="B121" s="190"/>
+      <c r="C121" s="190"/>
+    </row>
+    <row r="122" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="85"/>
       <c r="B122" s="35">
         <v>0</v>
@@ -3053,13 +3011,13 @@
       </c>
       <c r="E122" s="101"/>
     </row>
-    <row r="123" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="85"/>
       <c r="B123" s="87"/>
       <c r="C123" s="84"/>
       <c r="D123" s="101"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="43" t="s">
         <v>8</v>
       </c>
@@ -3069,39 +3027,44 @@
       </c>
       <c r="C124" s="44"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M125" s="7"/>
     </row>
-    <row r="126" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="192"/>
-      <c r="B126" s="192"/>
-      <c r="C126" s="192"/>
-      <c r="D126" s="192"/>
-      <c r="E126" s="192"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="192"/>
-      <c r="B127" s="192"/>
-      <c r="C127" s="192"/>
-      <c r="D127" s="192"/>
-      <c r="E127" s="192"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="192"/>
-      <c r="B128" s="192"/>
-      <c r="C128" s="192"/>
-      <c r="D128" s="192"/>
-      <c r="E128" s="192"/>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="192"/>
-      <c r="B129" s="192"/>
-      <c r="C129" s="192"/>
-      <c r="D129" s="192"/>
-      <c r="E129" s="192"/>
+    <row r="126" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="189"/>
+      <c r="B126" s="189"/>
+      <c r="C126" s="189"/>
+      <c r="D126" s="189"/>
+      <c r="E126" s="189"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A127" s="189"/>
+      <c r="B127" s="189"/>
+      <c r="C127" s="189"/>
+      <c r="D127" s="189"/>
+      <c r="E127" s="189"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A128" s="189"/>
+      <c r="B128" s="189"/>
+      <c r="C128" s="189"/>
+      <c r="D128" s="189"/>
+      <c r="E128" s="189"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="189"/>
+      <c r="B129" s="189"/>
+      <c r="C129" s="189"/>
+      <c r="D129" s="189"/>
+      <c r="E129" s="189"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A126:E129"/>
     <mergeCell ref="A120:C121"/>
@@ -3114,11 +3077,6 @@
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A112:B115"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="110" orientation="portrait" r:id="rId1"/>
@@ -3129,42 +3087,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="204"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
+      <c r="G1" s="202"/>
+      <c r="H1" s="202"/>
+      <c r="I1" s="202"/>
+      <c r="J1" s="202"/>
+      <c r="K1" s="202"/>
+      <c r="L1" s="202"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3188,7 +3146,7 @@
       <c r="M2" s="53"/>
       <c r="N2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3203,113 +3161,113 @@
       <c r="L3" s="57"/>
       <c r="M3" s="57"/>
     </row>
-    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="211" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="212"/>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
-      <c r="M4" s="213"/>
-    </row>
-    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="214"/>
-      <c r="B5" s="183"/>
-      <c r="C5" s="183"/>
-      <c r="D5" s="183"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="183"/>
-      <c r="J5" s="183"/>
-      <c r="K5" s="183"/>
-      <c r="L5" s="183"/>
-      <c r="M5" s="215"/>
-    </row>
-    <row r="6" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="216"/>
-      <c r="B6" s="217"/>
-      <c r="C6" s="217"/>
-      <c r="D6" s="217"/>
-      <c r="E6" s="217"/>
-      <c r="F6" s="217"/>
-      <c r="G6" s="217"/>
-      <c r="H6" s="217"/>
-      <c r="I6" s="217"/>
-      <c r="J6" s="217"/>
-      <c r="K6" s="217"/>
-      <c r="L6" s="217"/>
-      <c r="M6" s="218"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="210" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="211"/>
+      <c r="C4" s="211"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
+      <c r="M4" s="212"/>
+    </row>
+    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="213"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="196"/>
+      <c r="E5" s="196"/>
+      <c r="F5" s="196"/>
+      <c r="G5" s="196"/>
+      <c r="H5" s="196"/>
+      <c r="I5" s="196"/>
+      <c r="J5" s="196"/>
+      <c r="K5" s="196"/>
+      <c r="L5" s="196"/>
+      <c r="M5" s="214"/>
+    </row>
+    <row r="6" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="215"/>
+      <c r="B6" s="216"/>
+      <c r="C6" s="216"/>
+      <c r="D6" s="216"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="216"/>
+      <c r="H6" s="216"/>
+      <c r="I6" s="216"/>
+      <c r="J6" s="216"/>
+      <c r="K6" s="216"/>
+      <c r="L6" s="216"/>
+      <c r="M6" s="217"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="197" t="s">
+      <c r="B7" s="205" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="197" t="s">
+      <c r="C7" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="197" t="s">
+      <c r="D7" s="205" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="197" t="s">
+      <c r="E7" s="205" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="205" t="s">
+      <c r="F7" s="203" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="197" t="s">
+      <c r="G7" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="207" t="s">
+      <c r="H7" s="206" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="205" t="s">
+      <c r="I7" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="205" t="s">
+      <c r="J7" s="203" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="209" t="s">
+      <c r="K7" s="208" t="s">
         <v>59</v>
       </c>
       <c r="L7" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="203" t="s">
+      <c r="M7" s="201" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="197"/>
-      <c r="B8" s="198"/>
-      <c r="C8" s="197"/>
-      <c r="D8" s="198"/>
-      <c r="E8" s="197"/>
-      <c r="F8" s="206"/>
-      <c r="G8" s="197"/>
-      <c r="H8" s="208"/>
-      <c r="I8" s="206"/>
-      <c r="J8" s="206"/>
-      <c r="K8" s="210"/>
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="205"/>
+      <c r="B8" s="218"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="218"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="204"/>
+      <c r="G8" s="205"/>
+      <c r="H8" s="207"/>
+      <c r="I8" s="204"/>
+      <c r="J8" s="204"/>
+      <c r="K8" s="209"/>
       <c r="L8" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="M8" s="203"/>
-    </row>
-    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="201"/>
+    </row>
+    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="120">
         <v>1</v>
       </c>
@@ -3320,7 +3278,7 @@
         <v>86</v>
       </c>
       <c r="D9" s="120" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E9" s="142">
         <v>3.43</v>
@@ -3329,11 +3287,11 @@
         <v>182208.01</v>
       </c>
       <c r="G9" s="131">
-        <f>F9</f>
+        <f t="shared" ref="G9:G14" si="0">F9</f>
         <v>182208.01</v>
       </c>
       <c r="H9" s="123">
-        <f t="shared" ref="H9:H33" si="0">F9-G9</f>
+        <f t="shared" ref="H9:H33" si="1">F9-G9</f>
         <v>0</v>
       </c>
       <c r="I9" s="123">
@@ -3349,18 +3307,18 @@
         <v>0</v>
       </c>
       <c r="L9" s="126">
-        <f t="shared" ref="L9:L33" si="1">ROUND(SUM(H9:K9),0) + N9</f>
+        <f t="shared" ref="L9:L33" si="2">ROUND(SUM(H9:K9),0) + N9</f>
         <v>186280.01</v>
       </c>
       <c r="M9" s="127">
-        <f t="shared" ref="M9:M33" si="2">ROUND(L9*3%,0) + L9</f>
+        <f t="shared" ref="M9:M33" si="3">ROUND(L9*3%,0) + L9</f>
         <v>191868.01</v>
       </c>
       <c r="N9" s="42">
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="129">
         <f>A9+1</f>
         <v>2</v>
@@ -3372,7 +3330,7 @@
         <v>87</v>
       </c>
       <c r="D10" s="130" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E10" s="143">
         <v>2.95</v>
@@ -3381,31 +3339,31 @@
         <v>160211.01999999999</v>
       </c>
       <c r="G10" s="131">
-        <f>F10</f>
+        <f t="shared" si="0"/>
         <v>160211.01999999999</v>
       </c>
       <c r="H10" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I10" s="123">
-        <f t="shared" ref="I10:I33" si="3">IF(H10&gt;0,H10*3%,0)</f>
+        <f t="shared" ref="I10:I33" si="4">IF(H10&gt;0,H10*3%,0)</f>
         <v>0</v>
       </c>
       <c r="J10" s="124">
-        <f t="shared" ref="J10:J32" si="4">K$2*E10%</f>
+        <f t="shared" ref="J10:J32" si="5">K$2*E10%</f>
         <v>160211.42639500002</v>
       </c>
       <c r="K10" s="125">
-        <f t="shared" ref="K10:K32" si="5">G$2*E10/100</f>
+        <f t="shared" ref="K10:K32" si="6">G$2*E10/100</f>
         <v>0</v>
       </c>
       <c r="L10" s="126">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>160211.01999999999</v>
       </c>
       <c r="M10" s="127">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>165017.01999999999</v>
       </c>
       <c r="N10" s="42">
@@ -3414,9 +3372,9 @@
       </c>
       <c r="O10" s="42"/>
     </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="129">
-        <f t="shared" ref="A11:A32" si="6">A10+1</f>
+        <f t="shared" ref="A11:A32" si="7">A10+1</f>
         <v>3</v>
       </c>
       <c r="B11" s="129" t="s">
@@ -3426,7 +3384,7 @@
         <v>88</v>
       </c>
       <c r="D11" s="130" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E11" s="143">
         <f>5.78+1.02</f>
@@ -3436,51 +3394,51 @@
         <v>369301.03</v>
       </c>
       <c r="G11" s="131">
-        <f>F11</f>
+        <f t="shared" si="0"/>
         <v>369301.03</v>
       </c>
       <c r="H11" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I11" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="124">
+        <f t="shared" si="5"/>
+        <v>369300.91508000006</v>
+      </c>
+      <c r="K11" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="126">
+        <f t="shared" si="2"/>
+        <v>369301.03</v>
+      </c>
+      <c r="M11" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="124">
-        <f t="shared" si="4"/>
-        <v>369300.91508000006</v>
-      </c>
-      <c r="K11" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="126">
-        <f t="shared" si="1"/>
-        <v>369301.03</v>
-      </c>
-      <c r="M11" s="127">
-        <f t="shared" si="2"/>
         <v>380380.03</v>
       </c>
       <c r="N11" s="42">
-        <f t="shared" ref="N11:N33" si="7">N10+0.01</f>
+        <f t="shared" ref="N11:N32" si="8">N10+0.01</f>
         <v>0.03</v>
       </c>
       <c r="O11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="120">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="B12" s="120" t="s">
         <v>63</v>
       </c>
       <c r="C12" s="128" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D12" s="128"/>
       <c r="E12" s="142">
@@ -3490,42 +3448,42 @@
         <v>182327.04000000001</v>
       </c>
       <c r="G12" s="131">
-        <f>F12</f>
+        <f t="shared" si="0"/>
         <v>182327.04000000001</v>
       </c>
       <c r="H12" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I12" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="124">
+        <f t="shared" si="5"/>
+        <v>186279.72628300005</v>
+      </c>
+      <c r="K12" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="126">
+        <f t="shared" si="2"/>
+        <v>186280.04</v>
+      </c>
+      <c r="M12" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="124">
-        <f t="shared" si="4"/>
-        <v>186279.72628300005</v>
-      </c>
-      <c r="K12" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="126">
-        <f t="shared" si="1"/>
-        <v>186280.04</v>
-      </c>
-      <c r="M12" s="127">
-        <f t="shared" si="2"/>
         <v>191868.04</v>
       </c>
       <c r="N12" s="42">
+        <f t="shared" si="8"/>
+        <v>0.04</v>
+      </c>
+      <c r="P12" s="42"/>
+    </row>
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="120">
         <f t="shared" si="7"/>
-        <v>0.04</v>
-      </c>
-      <c r="P12" s="42"/>
-    </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="120">
-        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="B13" s="120" t="s">
@@ -3542,42 +3500,42 @@
         <v>160211.04999999999</v>
       </c>
       <c r="G13" s="131">
-        <f>F13</f>
+        <f t="shared" si="0"/>
         <v>160211.04999999999</v>
       </c>
       <c r="H13" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I13" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="124">
+        <f t="shared" si="5"/>
+        <v>160211.42639500002</v>
+      </c>
+      <c r="K13" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="126">
+        <f t="shared" si="2"/>
+        <v>160211.04999999999</v>
+      </c>
+      <c r="M13" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="124">
-        <f t="shared" si="4"/>
-        <v>160211.42639500002</v>
-      </c>
-      <c r="K13" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="126">
-        <f t="shared" si="1"/>
-        <v>160211.04999999999</v>
-      </c>
-      <c r="M13" s="127">
-        <f t="shared" si="2"/>
         <v>165017.04999999999</v>
       </c>
       <c r="N13" s="42">
+        <f t="shared" si="8"/>
+        <v>0.05</v>
+      </c>
+      <c r="P13" s="42"/>
+    </row>
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="129">
         <f t="shared" si="7"/>
-        <v>0.05</v>
-      </c>
-      <c r="P13" s="42"/>
-    </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="129">
-        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="B14" s="129" t="s">
@@ -3594,44 +3552,44 @@
         <v>302264.06</v>
       </c>
       <c r="G14" s="131">
-        <f>F14</f>
+        <f t="shared" si="0"/>
         <v>302264.06</v>
       </c>
       <c r="H14" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="124">
+        <f t="shared" si="5"/>
+        <v>309017.97158900008</v>
+      </c>
+      <c r="K14" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="126">
+        <f t="shared" si="2"/>
+        <v>309018.06</v>
+      </c>
+      <c r="M14" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="124">
-        <f t="shared" si="4"/>
-        <v>309017.97158900008</v>
-      </c>
-      <c r="K14" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="126">
-        <f t="shared" si="1"/>
-        <v>309018.06</v>
-      </c>
-      <c r="M14" s="127">
-        <f t="shared" si="2"/>
         <v>318289.06</v>
       </c>
       <c r="N14" s="42">
+        <f t="shared" si="8"/>
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="O14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="120">
         <f t="shared" si="7"/>
-        <v>6.0000000000000005E-2</v>
-      </c>
-      <c r="O14" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="120">
-        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="B15" s="120" t="s">
@@ -3651,40 +3609,40 @@
         <v>279558</v>
       </c>
       <c r="H15" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46501.070000000007</v>
       </c>
       <c r="I15" s="123">
+        <f t="shared" si="4"/>
+        <v>1395.0321000000001</v>
+      </c>
+      <c r="J15" s="124">
+        <f t="shared" si="5"/>
+        <v>186279.72628300005</v>
+      </c>
+      <c r="K15" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="126">
+        <f t="shared" si="2"/>
+        <v>234176.07</v>
+      </c>
+      <c r="M15" s="127">
         <f t="shared" si="3"/>
-        <v>1395.0321000000001</v>
-      </c>
-      <c r="J15" s="124">
-        <f t="shared" si="4"/>
-        <v>186279.72628300005</v>
-      </c>
-      <c r="K15" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="126">
-        <f t="shared" si="1"/>
-        <v>234176.07</v>
-      </c>
-      <c r="M15" s="127">
-        <f t="shared" si="2"/>
         <v>241201.07</v>
       </c>
       <c r="N15" s="42">
+        <f t="shared" si="8"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="120">
         <f t="shared" si="7"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="O15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="120">
-        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="B16" s="120" t="s">
@@ -3694,7 +3652,7 @@
         <v>92</v>
       </c>
       <c r="D16" s="128" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E16" s="142">
         <v>2.95</v>
@@ -3704,47 +3662,47 @@
       </c>
       <c r="G16" s="131"/>
       <c r="H16" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>280430.08000000002</v>
       </c>
       <c r="I16" s="123">
+        <f t="shared" si="4"/>
+        <v>8412.9024000000009</v>
+      </c>
+      <c r="J16" s="124">
+        <f t="shared" si="5"/>
+        <v>160211.42639500002</v>
+      </c>
+      <c r="K16" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="126">
+        <f t="shared" si="2"/>
+        <v>449054.08</v>
+      </c>
+      <c r="M16" s="127">
         <f t="shared" si="3"/>
-        <v>8412.9024000000009</v>
-      </c>
-      <c r="J16" s="124">
-        <f t="shared" si="4"/>
-        <v>160211.42639500002</v>
-      </c>
-      <c r="K16" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="126">
-        <f t="shared" si="1"/>
-        <v>449054.08</v>
-      </c>
-      <c r="M16" s="127">
-        <f t="shared" si="2"/>
         <v>462526.08</v>
       </c>
       <c r="N16" s="42">
+        <f t="shared" si="8"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="120">
         <f t="shared" si="7"/>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="120">
-        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="B17" s="120" t="s">
         <v>75</v>
       </c>
       <c r="C17" s="120" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D17" s="128" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E17" s="142">
         <v>5.69</v>
@@ -3757,37 +3715,37 @@
         <v>540897.09</v>
       </c>
       <c r="H17" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I17" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="124">
+        <f t="shared" si="5"/>
+        <v>309017.97158900008</v>
+      </c>
+      <c r="K17" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="126">
+        <f t="shared" si="2"/>
+        <v>309018.09000000003</v>
+      </c>
+      <c r="M17" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="124">
-        <f t="shared" si="4"/>
-        <v>309017.97158900008</v>
-      </c>
-      <c r="K17" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="126">
-        <f t="shared" si="1"/>
-        <v>309018.09000000003</v>
-      </c>
-      <c r="M17" s="127">
-        <f t="shared" si="2"/>
         <v>318289.09000000003</v>
       </c>
       <c r="N17" s="42">
+        <f t="shared" si="8"/>
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="120">
         <f t="shared" si="7"/>
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="120">
-        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="B18" s="120" t="s">
@@ -3797,7 +3755,7 @@
         <v>93</v>
       </c>
       <c r="D18" s="128" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E18" s="142">
         <v>3.43</v>
@@ -3809,47 +3767,47 @@
         <v>191868.1</v>
       </c>
       <c r="H18" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-5588</v>
       </c>
       <c r="I18" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="124">
+        <f t="shared" si="5"/>
+        <v>186279.72628300005</v>
+      </c>
+      <c r="K18" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="126">
+        <f t="shared" si="2"/>
+        <v>180692.1</v>
+      </c>
+      <c r="M18" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="124">
-        <f t="shared" si="4"/>
-        <v>186279.72628300005</v>
-      </c>
-      <c r="K18" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="126">
-        <f t="shared" si="1"/>
-        <v>180692.1</v>
-      </c>
-      <c r="M18" s="127">
-        <f t="shared" si="2"/>
         <v>186113.1</v>
       </c>
       <c r="N18" s="42">
+        <f t="shared" si="8"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="120">
         <f t="shared" si="7"/>
-        <v>9.9999999999999992E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="120">
-        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="B19" s="120" t="s">
         <v>76</v>
       </c>
       <c r="C19" s="120" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D19" s="128" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E19" s="142">
         <v>2.95</v>
@@ -3862,47 +3820,47 @@
         <v>160211.10999999999</v>
       </c>
       <c r="H19" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I19" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="124">
+        <f t="shared" si="5"/>
+        <v>160211.42639500002</v>
+      </c>
+      <c r="K19" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="126">
+        <f t="shared" si="2"/>
+        <v>160211.10999999999</v>
+      </c>
+      <c r="M19" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="124">
-        <f t="shared" si="4"/>
-        <v>160211.42639500002</v>
-      </c>
-      <c r="K19" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="126">
-        <f t="shared" si="1"/>
-        <v>160211.10999999999</v>
-      </c>
-      <c r="M19" s="127">
-        <f t="shared" si="2"/>
         <v>165017.10999999999</v>
       </c>
       <c r="N19" s="42">
+        <f t="shared" si="8"/>
+        <v>0.10999999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="120">
         <f t="shared" si="7"/>
-        <v>0.10999999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="120">
-        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="B20" s="120" t="s">
         <v>77</v>
       </c>
       <c r="C20" s="120" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E20" s="142">
         <f>5.69+0.51</f>
@@ -3915,37 +3873,37 @@
         <v>346814.12</v>
       </c>
       <c r="H20" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-10098</v>
       </c>
       <c r="I20" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="124">
+        <f t="shared" si="5"/>
+        <v>336715.54022000002</v>
+      </c>
+      <c r="K20" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="126">
+        <f t="shared" si="2"/>
+        <v>326618.12</v>
+      </c>
+      <c r="M20" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="124">
-        <f t="shared" si="4"/>
-        <v>336715.54022000002</v>
-      </c>
-      <c r="K20" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="126">
-        <f t="shared" si="1"/>
-        <v>326618.12</v>
-      </c>
-      <c r="M20" s="127">
-        <f t="shared" si="2"/>
         <v>336417.12</v>
       </c>
       <c r="N20" s="42">
+        <f t="shared" si="8"/>
+        <v>0.11999999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="120">
         <f t="shared" si="7"/>
-        <v>0.11999999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="120">
-        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="B21" s="120" t="s">
@@ -3955,7 +3913,7 @@
         <v>94</v>
       </c>
       <c r="D21" s="128" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E21" s="142">
         <v>3.43</v>
@@ -3968,37 +3926,37 @@
         <v>180873.13</v>
       </c>
       <c r="H21" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I21" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="124">
+        <f t="shared" si="5"/>
+        <v>186279.72628300005</v>
+      </c>
+      <c r="K21" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="126">
+        <f t="shared" si="2"/>
+        <v>186280.13</v>
+      </c>
+      <c r="M21" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="124">
-        <f t="shared" si="4"/>
-        <v>186279.72628300005</v>
-      </c>
-      <c r="K21" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="126">
-        <f t="shared" si="1"/>
-        <v>186280.13</v>
-      </c>
-      <c r="M21" s="127">
-        <f t="shared" si="2"/>
         <v>191868.13</v>
       </c>
       <c r="N21" s="42">
+        <f t="shared" si="8"/>
+        <v>0.12999999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="120">
         <f t="shared" si="7"/>
-        <v>0.12999999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="120">
-        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="B22" s="120" t="s">
@@ -4008,7 +3966,7 @@
         <v>95</v>
       </c>
       <c r="D22" s="128" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E22" s="142">
         <v>2.95</v>
@@ -4021,37 +3979,37 @@
         <v>160211.14000000001</v>
       </c>
       <c r="H22" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I22" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="124">
+        <f t="shared" si="5"/>
+        <v>160211.42639500002</v>
+      </c>
+      <c r="K22" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="126">
+        <f t="shared" si="2"/>
+        <v>160211.14000000001</v>
+      </c>
+      <c r="M22" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="124">
-        <f t="shared" si="4"/>
-        <v>160211.42639500002</v>
-      </c>
-      <c r="K22" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="126">
-        <f t="shared" si="1"/>
-        <v>160211.14000000001</v>
-      </c>
-      <c r="M22" s="127">
-        <f t="shared" si="2"/>
         <v>165017.14000000001</v>
       </c>
       <c r="N22" s="42">
+        <f t="shared" si="8"/>
+        <v>0.13999999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="129">
         <f t="shared" si="7"/>
-        <v>0.13999999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="129">
-        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="B23" s="129" t="s">
@@ -4061,7 +4019,7 @@
         <v>96</v>
       </c>
       <c r="D23" s="130" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E23" s="143">
         <f>5.69+0.51</f>
@@ -4075,37 +4033,37 @@
         <v>336716.15</v>
       </c>
       <c r="H23" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I23" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="124">
+        <f t="shared" si="5"/>
+        <v>336715.54022000002</v>
+      </c>
+      <c r="K23" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="126">
+        <f t="shared" si="2"/>
+        <v>336716.15</v>
+      </c>
+      <c r="M23" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="124">
-        <f t="shared" si="4"/>
-        <v>336715.54022000002</v>
-      </c>
-      <c r="K23" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="126">
-        <f t="shared" si="1"/>
-        <v>336716.15</v>
-      </c>
-      <c r="M23" s="127">
-        <f t="shared" si="2"/>
         <v>346817.15</v>
       </c>
       <c r="N23" s="42">
+        <f t="shared" si="8"/>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="129">
         <f t="shared" si="7"/>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="129">
-        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="B24" s="129" t="s">
@@ -4125,37 +4083,37 @@
         <v>191868.16</v>
       </c>
       <c r="H24" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-5588</v>
       </c>
       <c r="I24" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="124">
+        <f t="shared" si="5"/>
+        <v>186279.72628300005</v>
+      </c>
+      <c r="K24" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="126">
+        <f t="shared" si="2"/>
+        <v>180692.16</v>
+      </c>
+      <c r="M24" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="124">
-        <f t="shared" si="4"/>
-        <v>186279.72628300005</v>
-      </c>
-      <c r="K24" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="126">
-        <f t="shared" si="1"/>
-        <v>180692.16</v>
-      </c>
-      <c r="M24" s="127">
-        <f t="shared" si="2"/>
         <v>186113.16</v>
       </c>
       <c r="N24" s="42">
+        <f t="shared" si="8"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="120">
         <f t="shared" si="7"/>
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="120">
-        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="B25" s="120" t="s">
@@ -4165,7 +4123,7 @@
         <v>98</v>
       </c>
       <c r="D25" s="128" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E25" s="142">
         <v>2.95</v>
@@ -4178,37 +4136,37 @@
         <v>160211.17000000001</v>
       </c>
       <c r="H25" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I25" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="124">
+        <f t="shared" si="5"/>
+        <v>160211.42639500002</v>
+      </c>
+      <c r="K25" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="126">
+        <f t="shared" si="2"/>
+        <v>160211.17000000001</v>
+      </c>
+      <c r="M25" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="124">
-        <f t="shared" si="4"/>
-        <v>160211.42639500002</v>
-      </c>
-      <c r="K25" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="126">
-        <f t="shared" si="1"/>
-        <v>160211.17000000001</v>
-      </c>
-      <c r="M25" s="127">
-        <f t="shared" si="2"/>
         <v>165017.17000000001</v>
       </c>
       <c r="N25" s="42">
+        <f t="shared" si="8"/>
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="129">
         <f t="shared" si="7"/>
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="129">
-        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="B26" s="129" t="s">
@@ -4230,47 +4188,47 @@
         <v>344295.18</v>
       </c>
       <c r="H26" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I26" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="124">
+        <f t="shared" si="5"/>
+        <v>336715.54022000002</v>
+      </c>
+      <c r="K26" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="126">
+        <f t="shared" si="2"/>
+        <v>336716.18</v>
+      </c>
+      <c r="M26" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="124">
-        <f t="shared" si="4"/>
-        <v>336715.54022000002</v>
-      </c>
-      <c r="K26" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="126">
-        <f t="shared" si="1"/>
-        <v>336716.18</v>
-      </c>
-      <c r="M26" s="127">
-        <f t="shared" si="2"/>
         <v>346817.18</v>
       </c>
       <c r="N26" s="42">
+        <f t="shared" si="8"/>
+        <v>0.18000000000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="129">
         <f t="shared" si="7"/>
-        <v>0.18000000000000002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="129">
-        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="B27" s="129" t="s">
         <v>68</v>
       </c>
       <c r="C27" s="129" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D27" s="130" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E27" s="143">
         <v>3.43</v>
@@ -4280,47 +4238,47 @@
       </c>
       <c r="G27" s="131"/>
       <c r="H27" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>660257.18999999994</v>
       </c>
       <c r="I27" s="123">
+        <f t="shared" si="4"/>
+        <v>19807.715699999997</v>
+      </c>
+      <c r="J27" s="124">
+        <f t="shared" si="5"/>
+        <v>186279.72628300005</v>
+      </c>
+      <c r="K27" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="126">
+        <f t="shared" si="2"/>
+        <v>866345.19</v>
+      </c>
+      <c r="M27" s="127">
         <f t="shared" si="3"/>
-        <v>19807.715699999997</v>
-      </c>
-      <c r="J27" s="124">
-        <f t="shared" si="4"/>
-        <v>186279.72628300005</v>
-      </c>
-      <c r="K27" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="126">
-        <f t="shared" si="1"/>
-        <v>866345.19</v>
-      </c>
-      <c r="M27" s="127">
-        <f t="shared" si="2"/>
         <v>892335.19</v>
       </c>
       <c r="N27" s="42">
+        <f t="shared" si="8"/>
+        <v>0.19000000000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="129">
         <f t="shared" si="7"/>
-        <v>0.19000000000000003</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="129">
-        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="B28" s="153" t="s">
         <v>82</v>
       </c>
       <c r="C28" s="129" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D28" s="130" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E28" s="143">
         <v>2.95</v>
@@ -4333,37 +4291,37 @@
         <v>160211.20000000001</v>
       </c>
       <c r="H28" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I28" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="124">
+        <f t="shared" si="5"/>
+        <v>160211.42639500002</v>
+      </c>
+      <c r="K28" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="126">
+        <f t="shared" si="2"/>
+        <v>160211.20000000001</v>
+      </c>
+      <c r="M28" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="124">
-        <f t="shared" si="4"/>
-        <v>160211.42639500002</v>
-      </c>
-      <c r="K28" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="126">
-        <f t="shared" si="1"/>
-        <v>160211.20000000001</v>
-      </c>
-      <c r="M28" s="127">
-        <f t="shared" si="2"/>
         <v>165017.20000000001</v>
       </c>
       <c r="N28" s="42">
+        <f t="shared" si="8"/>
+        <v>0.20000000000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="129">
         <f t="shared" si="7"/>
-        <v>0.20000000000000004</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="129">
-        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="B29" s="153" t="s">
@@ -4384,37 +4342,37 @@
         <v>339450.21</v>
       </c>
       <c r="H29" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-9887</v>
       </c>
       <c r="I29" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="124">
+        <f t="shared" si="5"/>
+        <v>336715.54022000002</v>
+      </c>
+      <c r="K29" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="126">
+        <f t="shared" si="2"/>
+        <v>326829.21000000002</v>
+      </c>
+      <c r="M29" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="124">
-        <f t="shared" si="4"/>
-        <v>336715.54022000002</v>
-      </c>
-      <c r="K29" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="126">
-        <f t="shared" si="1"/>
-        <v>326829.21000000002</v>
-      </c>
-      <c r="M29" s="127">
-        <f t="shared" si="2"/>
         <v>336634.21</v>
       </c>
       <c r="N29" s="42">
+        <f t="shared" si="8"/>
+        <v>0.21000000000000005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="129">
         <f t="shared" si="7"/>
-        <v>0.21000000000000005</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="129">
-        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="B30" s="155" t="s">
@@ -4424,7 +4382,7 @@
         <v>101</v>
       </c>
       <c r="D30" s="130" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E30" s="143">
         <v>3.43</v>
@@ -4436,47 +4394,47 @@
         <v>140000</v>
       </c>
       <c r="H30" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>180730.21999999997</v>
       </c>
       <c r="I30" s="123">
+        <f t="shared" si="4"/>
+        <v>5421.9065999999993</v>
+      </c>
+      <c r="J30" s="124">
+        <f t="shared" si="5"/>
+        <v>186279.72628300005</v>
+      </c>
+      <c r="K30" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="126">
+        <f t="shared" si="2"/>
+        <v>372432.22</v>
+      </c>
+      <c r="M30" s="127">
         <f t="shared" si="3"/>
-        <v>5421.9065999999993</v>
-      </c>
-      <c r="J30" s="124">
-        <f t="shared" si="4"/>
-        <v>186279.72628300005</v>
-      </c>
-      <c r="K30" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L30" s="126">
-        <f t="shared" si="1"/>
-        <v>372432.22</v>
-      </c>
-      <c r="M30" s="127">
-        <f t="shared" si="2"/>
         <v>383605.22</v>
       </c>
       <c r="N30" s="42">
+        <f t="shared" si="8"/>
+        <v>0.22000000000000006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="129">
         <f t="shared" si="7"/>
-        <v>0.22000000000000006</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="129">
-        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="B31" s="155" t="s">
         <v>84</v>
       </c>
       <c r="C31" s="156" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D31" s="157" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E31" s="143">
         <v>2.95</v>
@@ -4489,37 +4447,37 @@
         <v>160211.23000000001</v>
       </c>
       <c r="H31" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I31" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="124">
+        <f t="shared" si="5"/>
+        <v>160211.42639500002</v>
+      </c>
+      <c r="K31" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="126">
+        <f t="shared" si="2"/>
+        <v>160211.23000000001</v>
+      </c>
+      <c r="M31" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="124">
-        <f t="shared" si="4"/>
-        <v>160211.42639500002</v>
-      </c>
-      <c r="K31" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="126">
-        <f t="shared" si="1"/>
-        <v>160211.23000000001</v>
-      </c>
-      <c r="M31" s="127">
-        <f t="shared" si="2"/>
         <v>165017.23000000001</v>
       </c>
       <c r="N31" s="42">
+        <f t="shared" si="8"/>
+        <v>0.23000000000000007</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="120">
         <f t="shared" si="7"/>
-        <v>0.23000000000000007</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="120">
-        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="B32" s="134" t="s">
@@ -4540,115 +4498,83 @@
         <v>301935.24</v>
       </c>
       <c r="H32" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I32" s="123">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="124">
+        <f t="shared" si="5"/>
+        <v>308474.88200799999</v>
+      </c>
+      <c r="K32" s="125">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="126">
+        <f t="shared" si="2"/>
+        <v>308475.24</v>
+      </c>
+      <c r="M32" s="127">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="124">
-        <f t="shared" si="4"/>
-        <v>308474.88200799999</v>
-      </c>
-      <c r="K32" s="125">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L32" s="126">
-        <f t="shared" si="1"/>
-        <v>308475.24</v>
-      </c>
-      <c r="M32" s="127">
-        <f t="shared" si="2"/>
         <v>317729.24</v>
       </c>
       <c r="N32" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="199" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" s="200"/>
-      <c r="C33" s="135" t="s">
-        <v>103</v>
-      </c>
+    <row r="33" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="219"/>
+      <c r="B33" s="220"/>
+      <c r="C33" s="135"/>
       <c r="D33" s="135"/>
       <c r="E33" s="121"/>
-      <c r="F33" s="132">
-        <v>158611.25</v>
-      </c>
-      <c r="G33" s="133">
-        <v>163369.25</v>
-      </c>
-      <c r="H33" s="123">
-        <f t="shared" si="0"/>
-        <v>-4758</v>
-      </c>
-      <c r="I33" s="123">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="124">
-        <f>J16</f>
-        <v>160211.42639500002</v>
-      </c>
-      <c r="K33" s="125">
-        <f>K16</f>
-        <v>0</v>
-      </c>
-      <c r="L33" s="126">
-        <f t="shared" si="1"/>
-        <v>155453.25</v>
-      </c>
-      <c r="M33" s="127">
-        <f t="shared" si="2"/>
-        <v>160117.25</v>
-      </c>
-      <c r="N33" s="42">
-        <f t="shared" si="7"/>
-        <v>0.25000000000000006</v>
-      </c>
-      <c r="O33" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="201" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" s="201"/>
-      <c r="C34" s="202"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="133"/>
+      <c r="H33" s="123"/>
+      <c r="I33" s="123"/>
+      <c r="J33" s="124"/>
+      <c r="K33" s="125"/>
+      <c r="L33" s="126"/>
+      <c r="M33" s="127"/>
+      <c r="N33" s="42"/>
+    </row>
+    <row r="34" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="221" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="221"/>
+      <c r="C34" s="222"/>
       <c r="D34" s="137"/>
       <c r="E34" s="145">
         <f>SUM(E9:E33)</f>
         <v>99.700000000000045</v>
       </c>
       <c r="F34" s="138">
-        <f t="shared" ref="F34:K34" si="8">SUM(F9:F33)</f>
-        <v>6647222.2500000009</v>
+        <f>SUM(F9:F33)</f>
+        <v>6488611.0000000009</v>
       </c>
       <c r="G34" s="139">
         <f>SUM(G9:G33)</f>
-        <v>5515222.6900000013</v>
+        <v>5351853.4400000013</v>
       </c>
       <c r="H34" s="139">
-        <f t="shared" si="8"/>
-        <v>1131999.56</v>
+        <f>SUM(H9:H33)</f>
+        <v>1136757.56</v>
       </c>
       <c r="I34" s="139">
-        <f t="shared" si="8"/>
+        <f>SUM(I9:I33)</f>
         <v>35037.556799999998</v>
       </c>
       <c r="J34" s="140">
-        <f t="shared" si="8"/>
-        <v>5574814.5489649996</v>
+        <f>SUM(J9:J33)</f>
+        <v>5414603.1225699997</v>
       </c>
       <c r="K34" s="139">
-        <f t="shared" si="8"/>
+        <f>SUM(K9:K33)</f>
         <v>0</v>
       </c>
       <c r="L34" s="141">
@@ -4657,91 +4583,99 @@
       </c>
       <c r="M34" s="141">
         <f>SUM(M9:M33)</f>
-        <v>6944108.2500000009</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6783991.0000000009</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="49"/>
       <c r="D35" s="49"/>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="192" t="str">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="189" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D37" s="192"/>
-      <c r="E37" s="192"/>
-      <c r="F37" s="192"/>
-      <c r="G37" s="192"/>
-      <c r="H37" s="192"/>
-      <c r="I37" s="192"/>
-      <c r="J37" s="192"/>
-      <c r="K37" s="192"/>
-      <c r="L37" s="192"/>
-    </row>
-    <row r="38" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="192"/>
-      <c r="D38" s="192"/>
-      <c r="E38" s="192"/>
-      <c r="F38" s="192"/>
-      <c r="G38" s="192"/>
-      <c r="H38" s="192"/>
-      <c r="I38" s="192"/>
-      <c r="J38" s="192"/>
-      <c r="K38" s="192"/>
-      <c r="L38" s="192"/>
-    </row>
-    <row r="39" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="192"/>
-      <c r="D39" s="192"/>
-      <c r="E39" s="192"/>
-      <c r="F39" s="192"/>
-      <c r="G39" s="192"/>
-      <c r="H39" s="192"/>
-      <c r="I39" s="192"/>
-      <c r="J39" s="192"/>
-      <c r="K39" s="192"/>
-      <c r="L39" s="192"/>
-    </row>
-    <row r="40" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="192"/>
-      <c r="D40" s="192"/>
-      <c r="E40" s="192"/>
-      <c r="F40" s="192"/>
-      <c r="G40" s="192"/>
-      <c r="H40" s="192"/>
-      <c r="I40" s="192"/>
-      <c r="J40" s="192"/>
-      <c r="K40" s="192"/>
-      <c r="L40" s="192"/>
-    </row>
-    <row r="41" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="192"/>
-      <c r="D41" s="192"/>
-      <c r="E41" s="192"/>
-      <c r="F41" s="192"/>
-      <c r="G41" s="192"/>
-      <c r="H41" s="192"/>
-      <c r="I41" s="192"/>
-      <c r="J41" s="192"/>
-      <c r="K41" s="192"/>
-      <c r="L41" s="192"/>
-    </row>
-    <row r="42" spans="1:15" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="192"/>
-      <c r="D42" s="192"/>
-      <c r="E42" s="192"/>
-      <c r="F42" s="192"/>
-      <c r="G42" s="192"/>
-      <c r="H42" s="192"/>
-      <c r="I42" s="192"/>
-      <c r="J42" s="192"/>
-      <c r="K42" s="192"/>
-      <c r="L42" s="192"/>
+      <c r="D37" s="189"/>
+      <c r="E37" s="189"/>
+      <c r="F37" s="189"/>
+      <c r="G37" s="189"/>
+      <c r="H37" s="189"/>
+      <c r="I37" s="189"/>
+      <c r="J37" s="189"/>
+      <c r="K37" s="189"/>
+      <c r="L37" s="189"/>
+    </row>
+    <row r="38" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="189"/>
+      <c r="D38" s="189"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="189"/>
+      <c r="G38" s="189"/>
+      <c r="H38" s="189"/>
+      <c r="I38" s="189"/>
+      <c r="J38" s="189"/>
+      <c r="K38" s="189"/>
+      <c r="L38" s="189"/>
+    </row>
+    <row r="39" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="189"/>
+      <c r="D39" s="189"/>
+      <c r="E39" s="189"/>
+      <c r="F39" s="189"/>
+      <c r="G39" s="189"/>
+      <c r="H39" s="189"/>
+      <c r="I39" s="189"/>
+      <c r="J39" s="189"/>
+      <c r="K39" s="189"/>
+      <c r="L39" s="189"/>
+    </row>
+    <row r="40" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="189"/>
+      <c r="D40" s="189"/>
+      <c r="E40" s="189"/>
+      <c r="F40" s="189"/>
+      <c r="G40" s="189"/>
+      <c r="H40" s="189"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="189"/>
+      <c r="K40" s="189"/>
+      <c r="L40" s="189"/>
+    </row>
+    <row r="41" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="189"/>
+      <c r="D41" s="189"/>
+      <c r="E41" s="189"/>
+      <c r="F41" s="189"/>
+      <c r="G41" s="189"/>
+      <c r="H41" s="189"/>
+      <c r="I41" s="189"/>
+      <c r="J41" s="189"/>
+      <c r="K41" s="189"/>
+      <c r="L41" s="189"/>
+    </row>
+    <row r="42" spans="1:14" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="189"/>
+      <c r="D42" s="189"/>
+      <c r="E42" s="189"/>
+      <c r="F42" s="189"/>
+      <c r="G42" s="189"/>
+      <c r="H42" s="189"/>
+      <c r="I42" s="189"/>
+      <c r="J42" s="189"/>
+      <c r="K42" s="189"/>
+      <c r="L42" s="189"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C37:L42"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="E1:L1"/>
     <mergeCell ref="I7:I8"/>
@@ -4751,14 +4685,6 @@
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="A4:M6"/>
-    <mergeCell ref="C37:L42"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4768,12 +4694,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B2:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="179" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C3" s="180"/>
       <c r="D3" s="172"/>
@@ -4781,48 +4707,48 @@
       <c r="F3" s="172"/>
       <c r="G3" s="173"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="181" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C4" s="182"/>
       <c r="G4" s="174"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="175"/>
       <c r="G5" s="174"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="219"/>
-      <c r="C6" s="220"/>
-      <c r="D6" s="220"/>
-      <c r="E6" s="220"/>
-      <c r="F6" s="220"/>
-      <c r="G6" s="221"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="219"/>
-      <c r="C7" s="220"/>
-      <c r="D7" s="220"/>
-      <c r="E7" s="220"/>
-      <c r="F7" s="220"/>
-      <c r="G7" s="221"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="219"/>
-      <c r="C8" s="220"/>
-      <c r="D8" s="220"/>
-      <c r="E8" s="220"/>
-      <c r="F8" s="220"/>
-      <c r="G8" s="221"/>
-    </row>
-    <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="222"/>
-      <c r="C9" s="223"/>
-      <c r="D9" s="223"/>
-      <c r="E9" s="223"/>
-      <c r="F9" s="223"/>
-      <c r="G9" s="224"/>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="223"/>
+      <c r="C6" s="224"/>
+      <c r="D6" s="224"/>
+      <c r="E6" s="224"/>
+      <c r="F6" s="224"/>
+      <c r="G6" s="225"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="223"/>
+      <c r="C7" s="224"/>
+      <c r="D7" s="224"/>
+      <c r="E7" s="224"/>
+      <c r="F7" s="224"/>
+      <c r="G7" s="225"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="223"/>
+      <c r="C8" s="224"/>
+      <c r="D8" s="224"/>
+      <c r="E8" s="224"/>
+      <c r="F8" s="224"/>
+      <c r="G8" s="225"/>
+    </row>
+    <row r="9" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="226"/>
+      <c r="C9" s="227"/>
+      <c r="D9" s="227"/>
+      <c r="E9" s="227"/>
+      <c r="F9" s="227"/>
+      <c r="G9" s="228"/>
     </row>
   </sheetData>
   <mergeCells count="1">
